--- a/data/export/2026-09-20-operations.xlsx
+++ b/data/export/2026-09-20-operations.xlsx
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -648,24 +648,24 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>07:13</t>
+          <t>07:16</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>68分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>06:21采样：该车到重点站唐陆公路龙东大道 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -704,12 +704,12 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -719,22 +719,22 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>1/9</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -772,29 +772,29 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>07:25</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>06:21采样：该车到重点站博兴路东陆路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -828,12 +828,12 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
@@ -853,12 +853,12 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>2/9</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -896,12 +896,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>06:21采样：该车到重点站新川路华东路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±9分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -952,12 +952,12 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -967,12 +967,12 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>3/9</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -1025,26 +1025,22 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：07:21采样，终点ETA 33分钟</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr"/>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1052,7 +1048,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1076,12 +1072,12 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -1091,22 +1087,22 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>3/9</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -1144,29 +1140,29 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数76分钟估算，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1176,7 +1172,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1200,12 +1196,12 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
@@ -1225,12 +1221,12 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>7/9</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1296,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1339,12 +1335,12 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1354,7 +1350,7 @@
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>5/9</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -1367,24 +1363,24 @@
       <c r="B8" s="2" t="inlineStr"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>沪A32298D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>06:48</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>06:55</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
-        </is>
-      </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -1397,34 +1393,34 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数80分钟估算，约±9分钟</t>
+          <t>07:21采样：该车到重点站唐陆公路锦绣东路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数29分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1438,7 +1434,7 @@
       <c r="U8" s="2" t="inlineStr"/>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>06:55</t>
+          <t>06:48</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1453,7 +1449,7 @@
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
@@ -1473,12 +1469,12 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>8/9</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -1491,24 +1487,24 @@
       <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>沪A12050A</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>06:55</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
-        </is>
-      </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -1521,30 +1517,34 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr"/>
+          <t>07:21采样：该车到重点站东陆路金海路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1558,7 +1558,7 @@
       <c r="U9" s="2" t="inlineStr"/>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:55</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -1568,17 +1568,17 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1588,13 +1588,17 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC9" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -1607,24 +1611,24 @@
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>沪A68397D</t>
+          <t>沪A12050A</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
-        </is>
-      </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -1637,34 +1641,30 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数74分钟估算，约±7分钟</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1678,7 +1678,7 @@
       <c r="U10" s="2" t="inlineStr"/>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1688,17 +1688,17 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1708,45 +1708,41 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC10" s="2" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>5/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1761,19 +1757,19 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>06:21采样：该车到重点站川周公路康沈路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数118分钟，约±5分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数74分钟估算，约±5分钟</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1783,12 +1779,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1802,7 +1798,7 @@
       <c r="U11" s="2" t="inlineStr"/>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1817,7 +1813,7 @@
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
@@ -1827,50 +1823,50 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>5/8</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1885,24 +1881,24 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>06:21采样：该车到重点站莱阳路东陆路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数117分钟，约±5分钟</t>
+          <t>07:21采样：该车到重点站东陆路金海路 ETA 20分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±8分钟</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1912,7 +1908,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1926,7 +1922,7 @@
       <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1961,40 +1957,40 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>4/8</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -2009,24 +2005,24 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数134分钟估算，约±10分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数77分钟估算，约±6分钟</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -2036,7 +2032,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2050,7 +2046,7 @@
       <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -2085,40 +2081,40 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>2/8</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2133,22 +2129,26 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr"/>
+          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±7分钟</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2170,7 +2170,7 @@
       <c r="U14" s="2" t="inlineStr"/>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2180,61 +2180,65 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC14" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2249,30 +2253,34 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr"/>
+          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2286,7 +2294,7 @@
       <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2296,17 +2304,17 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2316,41 +2324,45 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC15" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A02126A</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2365,34 +2377,30 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数134分钟估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2406,7 +2414,7 @@
       <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2416,17 +2424,17 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2436,45 +2444,41 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC16" s="2" t="inlineStr">
-        <is>
-          <t>134.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr"/>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>2/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2489,22 +2493,26 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr"/>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2512,7 +2520,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2526,7 +2534,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2536,61 +2544,65 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC17" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2605,19 +2617,19 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数132分钟估算，约±5分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±5分钟</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2627,12 +2639,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2646,7 +2658,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2671,40 +2683,40 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>1/8</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2714,7 +2726,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2724,39 +2736,39 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>07:20采样：该车到重点站迎春路金松路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2780,12 +2792,12 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
@@ -2805,40 +2817,40 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>11/20</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2853,19 +2865,19 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±5分钟</t>
+          <t>07:20采样：该车到重点站浦建路锦绣路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2875,12 +2887,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2894,7 +2906,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2909,7 +2921,7 @@
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
@@ -2929,40 +2941,40 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>8/20</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2977,34 +2989,34 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr"/>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±5分钟</t>
+          <t>07:20采样：该车到重点站丁香路锦绣路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数79分钟，约±7分钟</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3018,7 +3030,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -3033,7 +3045,7 @@
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
@@ -3053,40 +3065,40 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>4/20</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3101,34 +3113,34 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr"/>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数80分钟估算，约±8分钟</t>
+          <t>07:20采样：该车到重点站沪南路高科西路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数85分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3142,47 +3154,3971 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="AD22" s="2" t="inlineStr">
+        <is>
+          <t>15/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>134分钟</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站白桦路明月路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数85分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AD24" s="2" t="inlineStr">
+        <is>
+          <t>4/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AD25" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>135分钟</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站博兴路兰城路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数107分钟，约±11分钟</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AD26" s="2" t="inlineStr">
+        <is>
+          <t>8/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>136分钟</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站康沈路秀康路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数105分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AD27" s="2" t="inlineStr">
+        <is>
+          <t>11/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>132分钟</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站莱阳路东陆路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数110分钟，约±9分钟</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>2/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>138分钟</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站川周公路康沈路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数118分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>06:33</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AD29" s="2" t="inlineStr">
+        <is>
+          <t>14/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>123分钟</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站关岳路康达路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数112分钟，约±7分钟</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
+      <c r="AD30" s="2" t="inlineStr">
+        <is>
+          <t>1/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>142分钟</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站关岳路康达路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数131分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
+      <c r="AD31" s="2" t="inlineStr">
+        <is>
+          <t>16/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>134分钟</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站浦东大道东波路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数125分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AD32" s="2" t="inlineStr">
+        <is>
+          <t>4/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>136分钟</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数136分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AD33" s="2" t="inlineStr">
+        <is>
+          <t>11/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AD34" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>135分钟</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数135分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AD35" s="2" t="inlineStr">
+        <is>
+          <t>8/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>133分钟</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数133分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AD36" s="2" t="inlineStr">
+        <is>
+          <t>3/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>134分钟</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数134分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AD37" s="2" t="inlineStr">
+        <is>
+          <t>4/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>沪A66373D</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AD38" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>92分钟</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS末次终点ETA推算：07:20采样，终点ETA 22分钟</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>末次终点ETA兜底</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>85.5</t>
+        </is>
+      </c>
+      <c r="AD39" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>07:58</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>93分钟</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站五莲路荷泽路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数31分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AD40" s="2" t="inlineStr">
+        <is>
+          <t>14/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>92分钟</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站巨峰路成园路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AD41" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>08:02</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站巨峰路成园路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数41分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AD42" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
           <t>06:50</t>
         </is>
       </c>
-      <c r="W22" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>80分钟</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站金高路俱进路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数46分钟，约±7分钟</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X22" s="2" t="inlineStr">
+      <c r="X43" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="Y22" s="2" t="inlineStr">
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AD43" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>08:16</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站五莲路荷泽路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±7分钟</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AD44" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站金高路俱进路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AD45" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>79分钟</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站金杨路枣庄路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AD46" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Z22" s="2" t="inlineStr">
+      <c r="Z47" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC22" s="2" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
-      <c r="AD22" s="2" t="inlineStr">
-        <is>
-          <t>1/4</t>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD47" s="2" t="inlineStr">
+        <is>
+          <t>4/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>08:41</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站金杨路枣庄路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±8分钟</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AD48" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr"/>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>08:43</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AD49" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AD50" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>79分钟</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AD51" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr"/>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr"/>
+      <c r="AD52" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr"/>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AD53" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>79分钟</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>85.5</t>
+        </is>
+      </c>
+      <c r="AD54" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-20-operations.xlsx
+++ b/data/export/2026-09-20-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD54"/>
+  <dimension ref="A1:AD72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -454,7 +454,7 @@
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
-    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="22" customWidth="1" min="25" max="25"/>
     <col width="14" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
     <col width="18" customWidth="1" min="28" max="28"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -729,12 +729,12 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -843,22 +843,22 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -901,24 +901,24 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>07:33</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1020,27 +1020,31 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：07:21采样，终点ETA 33分钟</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1048,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1072,12 +1076,12 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -1097,12 +1101,12 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1145,24 +1149,24 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>07:53</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1172,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1211,12 +1215,12 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1226,7 +1230,7 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1269,19 +1273,19 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>107分钟</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数74分钟估算，约±5分钟</t>
+          <t>08:01采样：该车到重点站唐陆公路锦绣东路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数31分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1296,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1325,7 +1329,7 @@
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
@@ -1345,12 +1349,12 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1388,29 +1392,29 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>07:21采样：该车到重点站唐陆公路锦绣东路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数29分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1420,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1444,12 +1448,12 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
@@ -1459,22 +1463,22 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1512,29 +1516,29 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>07:21采样：该车到重点站东陆路金海路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1544,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1568,12 +1572,12 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
@@ -1593,12 +1597,12 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1668,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1703,7 +1707,7 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
@@ -1714,7 +1718,7 @@
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1757,19 +1761,19 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数74分钟估算，约±5分钟</t>
+          <t>08:01采样：该车到重点站唐陆公路锦绣东路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数31分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1784,7 +1788,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1813,7 +1817,7 @@
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
@@ -1833,12 +1837,12 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1881,26 +1885,22 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>07:21采样：该车到重点站东陆路金海路 ETA 20分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±8分钟</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：08:01采样，终点ETA 47分钟</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1908,7 +1908,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1932,17 +1932,17 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1952,17 +1952,13 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC12" s="2" t="inlineStr">
-        <is>
-          <t>76.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr"/>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2005,24 +2001,24 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数77分钟估算，约±6分钟</t>
+          <t>08:01采样：该车到重点站唐陆公路锦绣东路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -2032,7 +2028,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2061,7 +2057,7 @@
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
@@ -2081,12 +2077,12 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2129,24 +2125,24 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±7分钟</t>
+          <t>08:01采样：该车到重点站唐陆公路春雅路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -2156,7 +2152,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2185,7 +2181,7 @@
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
@@ -2205,12 +2201,12 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2253,24 +2249,24 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±9分钟</t>
+          <t>08:01采样：该车到重点站唐陆公路唐镇路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -2280,7 +2276,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2309,7 +2305,7 @@
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
@@ -2329,12 +2325,12 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2400,7 +2396,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2450,7 +2446,7 @@
       <c r="AC16" s="2" t="inlineStr"/>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2493,24 +2489,24 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±5分钟</t>
+          <t>08:01采样：该车到重点站东陆路金海路 ETA 19分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±6分钟</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2520,7 +2516,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2549,7 +2545,7 @@
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
@@ -2569,12 +2565,12 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2587,24 +2583,24 @@
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A31073D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
-        </is>
-      </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -2617,19 +2613,19 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±5分钟</t>
+          <t>08:01采样：该车到重点站新川路妙境路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2644,7 +2640,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2658,7 +2654,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2673,7 +2669,7 @@
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
@@ -2693,40 +2689,40 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2741,19 +2737,19 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站迎春路金松路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±5分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±5分钟</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2768,7 +2764,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2782,7 +2778,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2797,7 +2793,7 @@
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
@@ -2807,50 +2803,50 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>11/20</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2865,19 +2861,19 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站浦建路锦绣路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±5分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数76分钟估算，约±5分钟</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2892,7 +2888,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2906,7 +2902,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2921,7 +2917,7 @@
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
@@ -2931,50 +2927,50 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>8/20</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A08953A</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2989,34 +2985,30 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr"/>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站丁香路锦绣路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数79分钟，约±7分钟</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3030,7 +3022,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -3040,17 +3032,17 @@
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3060,45 +3052,41 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC21" s="2" t="inlineStr">
-        <is>
-          <t>134.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr"/>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>4/20</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3113,34 +3101,34 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr"/>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站沪南路高科西路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数85分钟，约±5分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±8分钟</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3154,7 +3142,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3169,7 +3157,7 @@
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
@@ -3179,50 +3167,50 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>15/20</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A12050A</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3255,12 +3243,12 @@
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3274,7 +3262,7 @@
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3299,7 +3287,7 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
@@ -3310,7 +3298,7 @@
       <c r="AC23" s="2" t="inlineStr"/>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -3323,24 +3311,24 @@
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>06:41</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -3353,34 +3341,30 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>161分钟</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站白桦路明月路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数85分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：08:01采样，终点ETA 50分钟</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3394,7 +3378,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3404,17 +3388,17 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3424,17 +3408,13 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC24" s="2" t="inlineStr">
-        <is>
-          <t>134.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr"/>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>4/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -3447,24 +3427,24 @@
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -3477,19 +3457,19 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：08:01采样，终点ETA 26分钟</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr"/>
@@ -3500,7 +3480,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3514,7 +3494,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3524,17 +3504,17 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3544,13 +3524,17 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC25" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -3563,7 +3547,7 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -3573,7 +3557,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3593,34 +3577,30 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站博兴路兰城路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数107分钟，约±11分钟</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：08:01采样，终点ETA 36分钟</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3634,7 +3614,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3649,7 +3629,7 @@
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -3669,12 +3649,12 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>8/20</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -3687,7 +3667,7 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3697,7 +3677,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3717,19 +3697,19 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站康沈路秀康路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数105分钟，约±5分钟</t>
+          <t>08:01采样：该车到重点站云山路碧云路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数53分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3739,12 +3719,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3758,7 +3738,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3793,12 +3773,12 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>11/20</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -3811,7 +3791,7 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3821,7 +3801,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -3841,34 +3821,30 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站莱阳路东陆路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数110分钟，约±9分钟</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3882,7 +3858,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3892,17 +3868,17 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3912,17 +3888,13 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC28" s="2" t="inlineStr">
-        <is>
-          <t>132.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr"/>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>2/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -3935,24 +3907,24 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -3965,19 +3937,19 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站川周公路康沈路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数118分钟，约±5分钟</t>
+          <t>08:01采样：该车到重点站沪南路北中路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数53分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3987,12 +3959,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:33</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -4006,7 +3978,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -4041,12 +4013,12 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>14/20</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -4059,7 +4031,7 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -4069,7 +4041,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -4089,34 +4061,30 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>123分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站关岳路康达路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数112分钟，约±7分钟</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4130,7 +4098,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4140,17 +4108,17 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4160,17 +4128,13 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC30" s="2" t="inlineStr">
-        <is>
-          <t>123.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr"/>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>1/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4183,24 +4147,24 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4213,19 +4177,19 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站关岳路康达路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数131分钟，约±5分钟</t>
+          <t>08:01采样：该车到重点站迎春路长柳路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数77分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -4235,12 +4199,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4254,7 +4218,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4289,12 +4253,12 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>16/20</t>
+          <t>17/27</t>
         </is>
       </c>
     </row>
@@ -4307,24 +4271,24 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4337,19 +4301,19 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站浦东大道东波路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数125分钟，约±5分钟</t>
+          <t>08:01采样：该车到重点站沪南路高科西路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数79分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -4359,12 +4323,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4378,7 +4342,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4413,12 +4377,12 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>4/20</t>
+          <t>14/27</t>
         </is>
       </c>
     </row>
@@ -4431,24 +4395,24 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>07:24</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4461,34 +4425,34 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数136分钟估算，约±5分钟</t>
+          <t>08:01采样：该车到重点站白桦路明月路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数91分钟，约±6分钟</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4502,7 +4466,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4517,7 +4481,7 @@
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
@@ -4537,12 +4501,12 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>11/20</t>
+          <t>14/27</t>
         </is>
       </c>
     </row>
@@ -4555,24 +4519,24 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4585,30 +4549,34 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr"/>
+          <t>08:01采样：该车到重点站沪南路华夏西路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数95分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:33</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4622,7 +4590,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4632,17 +4600,17 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4652,13 +4620,17 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC34" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>19/27</t>
         </is>
       </c>
     </row>
@@ -4671,7 +4643,7 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4681,7 +4653,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4701,34 +4673,34 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数135分钟估算，约±5分钟</t>
+          <t>07:40采样：该车到重点站康沈路秀康路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数99分钟，约±8分钟</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4742,7 +4714,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4757,7 +4729,7 @@
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
@@ -4777,12 +4749,12 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>8/20</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -4795,24 +4767,24 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4825,19 +4797,19 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数133分钟估算，约±5分钟</t>
+          <t>08:01采样：该车到重点站沪南路华夏西路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数99分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4847,12 +4819,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4866,7 +4838,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4881,7 +4853,7 @@
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4901,12 +4873,12 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>3/20</t>
+          <t>18/27</t>
         </is>
       </c>
     </row>
@@ -4919,24 +4891,24 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4949,34 +4921,34 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数134分钟估算，约±10分钟</t>
+          <t>08:01采样：该车到重点站金杨路云山路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数94分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4990,7 +4962,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -5005,7 +4977,7 @@
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
@@ -5025,12 +4997,12 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>4/20</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -5043,24 +5015,24 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A66373D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -5073,30 +5045,34 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr"/>
+          <t>08:01采样：该车到重点站康沈路秀康路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数109分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5110,7 +5086,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5120,17 +5096,17 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5140,41 +5116,45 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC38" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>14/27</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -5189,30 +5169,30 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：07:20采样，终点ETA 22分钟</t>
+          <t>尚无满足±5分钟标准的终点ETA</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5226,7 +5206,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5236,65 +5216,61 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr">
-        <is>
-          <t>85.5</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr"/>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5309,19 +5285,19 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站五莲路荷泽路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数31分钟，约±5分钟</t>
+          <t>08:01采样：该车到重点站康沈路秀康路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数109分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -5331,12 +5307,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5350,7 +5326,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5385,40 +5361,40 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>10/27</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5433,19 +5409,19 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站巨峰路成园路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±5分钟</t>
+          <t>08:01采样：该车到重点站莱阳路东陆路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数117分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -5455,12 +5431,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5474,7 +5450,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5509,40 +5485,40 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5557,34 +5533,34 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站巨峰路成园路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数41分钟，约±5分钟</t>
+          <t>08:01采样：该车到重点站川周公路康沈路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数120分钟，约±7分钟</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5598,7 +5574,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5633,40 +5609,40 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>9/27</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5681,34 +5657,30 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr"/>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站金高路俱进路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数46分钟，约±7分钟</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5722,7 +5694,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5732,17 +5704,17 @@
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5752,45 +5724,41 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC43" s="2" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A58633D</t>
+          <t>沪A66373D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5805,34 +5773,30 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>08:16</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr"/>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站五莲路荷泽路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±7分钟</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5846,7 +5810,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5856,17 +5820,17 @@
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5876,45 +5840,41 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC44" s="2" t="inlineStr">
-        <is>
-          <t>86.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5929,19 +5889,19 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr"/>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站金高路俱进路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数136分钟估算，约±5分钟</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5951,12 +5911,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5970,7 +5930,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5985,7 +5945,7 @@
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -6005,40 +5965,40 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -6053,34 +6013,34 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr"/>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站金杨路枣庄路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±5分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数130分钟估算，约±7分钟</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6094,7 +6054,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -6109,7 +6069,7 @@
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -6129,40 +6089,40 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -6177,34 +6137,34 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr"/>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±5分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数144分钟估算，约±13分钟</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6218,7 +6178,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6228,7 +6188,7 @@
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
@@ -6253,40 +6213,40 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>12/27</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6301,34 +6261,30 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr"/>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站金杨路枣庄路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±8分钟</t>
-        </is>
-      </c>
-      <c r="N48" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6342,7 +6298,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6352,17 +6308,17 @@
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6372,45 +6328,41 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC48" s="2" t="inlineStr">
-        <is>
-          <t>86.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr"/>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -6425,34 +6377,34 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr"/>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±5分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数136分钟估算，约±7分钟</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6466,7 +6418,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6501,40 +6453,40 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A57051D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6549,34 +6501,30 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr"/>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N50" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6590,7 +6538,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6600,17 +6548,17 @@
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6620,17 +6568,13 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC50" s="2" t="inlineStr">
-        <is>
-          <t>84.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr"/>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -6643,24 +6587,24 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -6673,34 +6617,30 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>107分钟</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr"/>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±8分钟</t>
-        </is>
-      </c>
-      <c r="N51" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：07:30采样，终点ETA 26分钟</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6714,7 +6654,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6724,12 +6664,12 @@
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
@@ -6739,22 +6679,22 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6767,7 +6707,7 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -6777,7 +6717,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -6792,35 +6732,39 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>107分钟</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr"/>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6834,7 +6778,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6844,33 +6788,37 @@
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC52" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6883,7 +6831,7 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -6893,7 +6841,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -6908,39 +6856,39 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr"/>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6954,7 +6902,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6964,12 +6912,12 @@
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -6979,22 +6927,22 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -7007,24 +6955,24 @@
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>08:03</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -7037,26 +6985,22 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr"/>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N54" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：08:00采样，终点ETA 12分钟</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -7064,7 +7008,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -7078,47 +7022,2255 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>末次终点ETA兜底</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AD54" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>08:27</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>97分钟</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>08:00采样：该车到重点站金杨路金口路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数21分钟，约±7分钟</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="AD55" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr"/>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>88分钟</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>86.5</t>
+        </is>
+      </c>
+      <c r="AD56" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr"/>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>08:36</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>96分钟</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>08:00采样：该车到重点站五莲路荷泽路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="AD57" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr"/>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>90分钟</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>08:00采样：该车到重点站金高路俱进路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数29分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AD58" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr"/>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>88分钟</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>08:00采样：该车到重点站五莲路荷泽路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数29分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AD59" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr"/>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>88分钟</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>08:00采样：该车到重点站巨峰路成园路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数42分钟，约±6分钟</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AD60" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr"/>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>91分钟</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>08:00采样：该车到重点站巨峰路成园路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD61" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr"/>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>08:59</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>89分钟</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>08:00采样：该车到重点站金高路俱进路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AD62" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr"/>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>08:00采样：该车到重点站巨峰路成园路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数42分钟，约±6分钟</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD63" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr"/>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AD64" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr"/>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>08:00采样：该车到重点站金杨路枣庄路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD65" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>79分钟</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>08:00采样：该车到重点站杨高北路夏碧路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AD66" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr"/>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
           <t>08:03</t>
         </is>
       </c>
-      <c r="W54" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>79分钟</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X54" s="2" t="inlineStr">
+      <c r="X67" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="Y54" s="2" t="inlineStr">
+      <c r="Y67" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Z54" s="2" t="inlineStr">
+      <c r="Z67" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
+      <c r="AA67" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB54" s="2" t="inlineStr">
+      <c r="AB67" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AC54" s="2" t="inlineStr">
-        <is>
-          <t>85.5</t>
-        </is>
-      </c>
-      <c r="AD54" s="2" t="inlineStr">
-        <is>
-          <t>9/15</t>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AD67" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr"/>
+      <c r="AD68" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr"/>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr"/>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="AD69" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr"/>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>89分钟</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数89分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AD70" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr"/>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr"/>
+      <c r="AD71" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr"/>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>86.5</t>
+        </is>
+      </c>
+      <c r="AD72" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-20-operations.xlsx
+++ b/data/export/2026-09-20-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD72"/>
+  <dimension ref="A1:AD80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -437,7 +437,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
@@ -447,14 +447,14 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="36" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
-    <col width="22" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
     <col width="14" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
     <col width="18" customWidth="1" min="28" max="28"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -729,12 +729,12 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -853,12 +853,12 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1273,19 +1273,19 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>107分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>08:01采样：该车到重点站唐陆公路锦绣东路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数31分钟，约±5分钟</t>
+          <t>同车下一次反向发车09:10，减去该车自身同类时段历史终点停站中位数11分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>同车反向发车反推</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
@@ -1339,22 +1339,22 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1521,24 +1521,24 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1587,22 +1587,22 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1640,27 +1640,31 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -1668,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1692,17 +1696,17 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1712,13 +1716,17 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC10" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1756,29 +1764,29 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>08:01采样：该车到重点站唐陆公路锦绣东路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数31分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1788,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1812,12 +1820,12 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
@@ -1827,22 +1835,22 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1880,27 +1888,31 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:01采样，终点ETA 47分钟</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1908,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1932,33 +1944,37 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC12" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2017,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -2013,7 +2029,7 @@
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>08:01采样：该车到重点站唐陆公路锦绣东路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±5分钟</t>
+          <t>08:19采样：该车到重点站唐陆公路川桥路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数24分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -2028,7 +2044,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2082,7 +2098,7 @@
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2125,24 +2141,24 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>08:01采样：该车到重点站唐陆公路春雅路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±5分钟</t>
+          <t>08:19采样：该车到重点站唐陆公路龙东大道 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±6分钟</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -2152,7 +2168,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2201,12 +2217,12 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2249,19 +2265,19 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>08:01采样：该车到重点站唐陆公路唐镇路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±5分钟</t>
+          <t>08:19采样：该车到重点站唐陆公路龙东大道 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数42分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2276,7 +2292,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2325,12 +2341,12 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2412,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2489,24 +2505,24 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>08:01采样：该车到重点站东陆路金海路 ETA 19分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±6分钟</t>
+          <t>08:19采样：该车到重点站唐陆公路川桥路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2516,7 +2532,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2565,12 +2581,12 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2613,19 +2629,19 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>08:01采样：该车到重点站新川路妙境路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±5分钟</t>
+          <t>08:19采样：该车到重点站德川路华夏东路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2640,7 +2656,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2689,12 +2705,12 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2780,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2861,19 +2877,19 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数76分钟估算，约±5分钟</t>
+          <t>08:19采样：该车到重点站新川路华东路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2888,7 +2904,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2917,7 +2933,7 @@
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
@@ -2937,12 +2953,12 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3008,7 +3024,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3128,7 +3144,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3195,24 +3211,24 @@
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>沪A12050A</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>08:55</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
-        </is>
-      </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -3225,30 +3241,34 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr"/>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr"/>
+          <t>按该车自身同方向、同类时段历史全程时间中位数74分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3262,7 +3282,7 @@
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3272,17 +3292,17 @@
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3292,41 +3312,45 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC23" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A12050A</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3341,30 +3365,30 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>161分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:01采样，终点ETA 50分钟</t>
+          <t>尚无满足±5分钟标准的终点ETA</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3378,7 +3402,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3393,7 +3417,7 @@
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -3403,46 +3427,50 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3457,30 +3485,34 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:01采样，终点ETA 26分钟</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr"/>
+          <t>按该车自身同方向、同类时段历史全程时间中位数75分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3494,7 +3526,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3504,12 +3536,12 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
@@ -3519,50 +3551,50 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3577,22 +3609,26 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:01采样，终点ETA 36分钟</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr"/>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3600,7 +3636,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3614,7 +3650,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3624,12 +3660,12 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -3639,22 +3675,22 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3703,7 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3677,7 +3713,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3692,29 +3728,29 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>161分钟</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>08:01采样：该车到重点站云山路碧云路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数53分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
@@ -3724,7 +3760,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3738,7 +3774,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3748,12 +3784,12 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
@@ -3763,22 +3799,22 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -3791,7 +3827,7 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3801,7 +3837,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -3816,27 +3852,31 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3844,7 +3884,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3858,7 +3898,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3868,17 +3908,17 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3888,13 +3928,17 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC28" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -3907,7 +3951,7 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3917,7 +3961,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3932,39 +3976,39 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>08:01采样：该车到重点站沪南路北中路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数53分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3978,7 +4022,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3988,12 +4032,12 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
@@ -4013,12 +4057,12 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4075,7 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -4041,7 +4085,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -4056,27 +4100,31 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4084,7 +4132,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4098,7 +4146,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4108,17 +4156,17 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4128,13 +4176,17 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC30" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -4147,7 +4199,7 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -4157,7 +4209,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -4167,44 +4219,40 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq29推进至seq40，推进11站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>148分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>08:01采样：该车到重点站迎春路长柳路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数77分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4212,13 +4260,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R31" s="2" t="inlineStr"/>
-      <c r="S31" s="2" t="inlineStr"/>
-      <c r="T31" s="2" t="inlineStr"/>
-      <c r="U31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>物理seq32（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq32映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±10分钟；反向位置锦绣路花木路 ETA 7分钟参与校验</t>
+        </is>
+      </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4228,17 +4292,17 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4248,17 +4312,13 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC31" s="2" t="inlineStr">
-        <is>
-          <t>148.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr"/>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>17/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4271,24 +4331,24 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4301,19 +4361,19 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>147分钟</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>08:01采样：该车到重点站沪南路高科西路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数79分钟，约±5分钟</t>
+          <t>08:18采样：该车到重点站沪南路御桥路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数40分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -4328,7 +4388,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4342,7 +4402,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4377,12 +4437,12 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>14/27</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -4395,24 +4455,24 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4425,34 +4485,30 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>147分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>08:01采样：该车到重点站白桦路明月路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数91分钟，约±6分钟</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
           <t>06:40</t>
-        </is>
-      </c>
-      <c r="P33" s="2" t="inlineStr">
-        <is>
-          <t>08:01</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4466,7 +4522,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4476,17 +4532,17 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4496,17 +4552,13 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC33" s="2" t="inlineStr">
-        <is>
-          <t>147.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr"/>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>14/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4519,24 +4571,24 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4549,19 +4601,19 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>151分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>08:01采样：该车到重点站沪南路华夏西路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数95分钟，约±5分钟</t>
+          <t>08:18采样：该车到重点站沪南路北中路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4571,12 +4623,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:33</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4590,7 +4642,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4625,12 +4677,12 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>19/27</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4695,7 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4653,7 +4705,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4673,34 +4725,34 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>07:40采样：该车到重点站康沈路秀康路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数99分钟，约±8分钟</t>
+          <t>08:18采样：该车到重点站锦绣路罗山路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±6分钟</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4714,7 +4766,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4749,12 +4801,12 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -4767,24 +4819,24 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4797,19 +4849,19 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>150分钟</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>08:01采样：该车到重点站沪南路华夏西路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数99分钟，约±5分钟</t>
+          <t>08:18采样：该车到重点站迎春路长柳路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数75分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4819,12 +4871,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4838,7 +4890,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4873,12 +4925,12 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>18/27</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -4891,24 +4943,24 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4921,19 +4973,19 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>157分钟</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>08:01采样：该车到重点站金杨路云山路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数94分钟，约±5分钟</t>
+          <t>08:18采样：该车到重点站沪南路高科西路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数83分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4943,12 +4995,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:33</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4962,7 +5014,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4997,12 +5049,12 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>157.0</t>
         </is>
       </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -5015,7 +5067,7 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -5025,7 +5077,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -5045,34 +5097,34 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>147分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>08:01采样：该车到重点站康沈路秀康路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数109分钟，约±5分钟</t>
+          <t>07:40采样：该车到重点站康沈路秀康路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数99分钟，约±8分钟</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5086,7 +5138,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5121,12 +5173,12 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>14/27</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -5139,24 +5191,24 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -5169,22 +5221,26 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>158分钟</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr"/>
+          <t>08:18采样：该车到重点站沪南路高科西路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5192,7 +5248,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5206,7 +5262,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5216,17 +5272,17 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5236,13 +5292,17 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -5255,24 +5315,24 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -5285,19 +5345,19 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>08:01采样：该车到重点站康沈路秀康路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数109分钟，约±5分钟</t>
+          <t>08:18采样：该车到重点站丁香路锦绣路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数81分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -5307,12 +5367,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5326,7 +5386,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5361,12 +5421,12 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>10/27</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -5379,24 +5439,24 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -5409,19 +5469,19 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>08:01采样：该车到重点站莱阳路东陆路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数117分钟，约±5分钟</t>
+          <t>08:18采样：该车到重点站沪南路华夏西路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数93分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -5431,12 +5491,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5450,7 +5510,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5485,12 +5545,12 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -5503,24 +5563,24 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -5533,34 +5593,30 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>08:01采样：该车到重点站川周公路康沈路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数120分钟，约±7分钟</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5574,7 +5630,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5584,17 +5640,17 @@
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5604,17 +5660,13 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC42" s="2" t="inlineStr">
-        <is>
-          <t>141.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr"/>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5679,7 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -5637,7 +5689,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -5657,30 +5709,34 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr"/>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr"/>
+          <t>08:18采样：该车到重点站沪南路华夏西路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数94分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5694,7 +5750,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5704,17 +5760,17 @@
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5724,13 +5780,17 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC43" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -5743,7 +5803,7 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A66373D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -5753,7 +5813,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -5773,30 +5833,34 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr"/>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr"/>
+          <t>08:18采样：该车到重点站金杨路云山路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数94分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5810,7 +5874,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5820,17 +5884,17 @@
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5840,13 +5904,17 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC44" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -5859,24 +5927,24 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -5889,34 +5957,34 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr"/>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数136分钟估算，约±5分钟</t>
+          <t>08:18采样：该车到重点站康沈路秀康路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数110分钟，约±8分钟</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5930,7 +5998,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5945,7 +6013,7 @@
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -5965,12 +6033,12 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -5983,7 +6051,7 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -5993,7 +6061,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -6013,34 +6081,34 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr"/>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数130分钟估算，约±7分钟</t>
+          <t>08:18采样：该车到重点站康沈路秀康路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数121分钟，约±15分钟</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6054,7 +6122,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -6064,12 +6132,12 @@
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -6089,12 +6157,12 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -6107,24 +6175,24 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A66373D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -6137,34 +6205,30 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr"/>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数144分钟估算，约±13分钟</t>
-        </is>
-      </c>
-      <c r="N47" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6178,7 +6242,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6188,17 +6252,17 @@
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6208,17 +6272,13 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC47" s="2" t="inlineStr">
-        <is>
-          <t>144.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr"/>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>12/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6231,7 +6291,7 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -6241,7 +6301,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -6261,30 +6321,34 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr"/>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N48" s="2" t="inlineStr"/>
+          <t>08:18采样：该车到重点站莱阳路东陆路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数118分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6298,7 +6362,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6308,17 +6372,17 @@
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6328,13 +6392,17 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC48" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -6347,7 +6415,7 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -6357,7 +6425,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -6377,24 +6445,24 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr"/>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数136分钟估算，约±7分钟</t>
+          <t>08:18采样：该车到重点站川周公路康沈路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数111分钟，约±6分钟</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
@@ -6404,7 +6472,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6418,7 +6486,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6433,7 +6501,7 @@
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
@@ -6453,12 +6521,12 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -6471,24 +6539,24 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A57051D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>08:35</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -6501,30 +6569,34 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr"/>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N50" s="2" t="inlineStr"/>
+          <t>08:18采样：该车到重点站关岳路康达路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数132分钟，约±13分钟</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6538,7 +6610,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6548,17 +6620,17 @@
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6568,41 +6640,45 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC50" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6617,30 +6693,30 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>107分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr"/>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：07:30采样，终点ETA 26分钟</t>
+          <t>尚无满足±5分钟标准的终点ETA</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6654,7 +6730,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6664,65 +6740,61 @@
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC51" s="2" t="inlineStr">
-        <is>
-          <t>93.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr"/>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6732,39 +6804,39 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>107分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr"/>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数136分钟估算，约±7分钟</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6778,7 +6850,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6788,12 +6860,12 @@
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6803,50 +6875,50 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A57051D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6856,39 +6928,35 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr"/>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N53" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6902,7 +6970,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6912,65 +6980,61 @@
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC53" s="2" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr"/>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6985,30 +7049,34 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr"/>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:00采样，终点ETA 12分钟</t>
-        </is>
-      </c>
-      <c r="N54" s="2" t="inlineStr"/>
+          <t>按该车自身同方向、同类时段历史全程时间中位数135分钟估算，约±14分钟</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -7022,7 +7090,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -7032,12 +7100,12 @@
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -7057,40 +7125,40 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -7105,34 +7173,34 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>97分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr"/>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>08:00采样：该车到重点站金杨路金口路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数21分钟，约±7分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数129分钟估算，约±5分钟</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7146,7 +7214,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -7161,7 +7229,7 @@
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
@@ -7171,22 +7239,22 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -7199,24 +7267,24 @@
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A58633D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>06:50</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -7224,39 +7292,35 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>107分钟</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr"/>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：07:30采样，终点ETA 26分钟</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7270,7 +7334,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7280,12 +7344,12 @@
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
@@ -7305,12 +7369,12 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -7323,7 +7387,7 @@
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -7333,7 +7397,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -7353,34 +7417,30 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>96分钟</t>
+          <t>106分钟</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr"/>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>08:00采样：该车到重点站五莲路荷泽路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N57" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：08:00采样，终点ETA 10分钟</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7394,7 +7454,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7409,7 +7469,7 @@
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -7419,22 +7479,22 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -7447,7 +7507,7 @@
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -7457,7 +7517,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -7472,29 +7532,29 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr"/>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>08:00采样：该车到重点站金高路俱进路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数29分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
@@ -7504,7 +7564,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7518,7 +7578,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7528,12 +7588,12 @@
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -7543,12 +7603,12 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7571,7 +7631,7 @@
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -7581,7 +7641,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -7601,34 +7661,30 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr"/>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>08:00采样：该车到重点站五莲路荷泽路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数29分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N59" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：08:00采样，终点ETA 12分钟</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7642,7 +7698,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7657,7 +7713,7 @@
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7667,22 +7723,22 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -7695,24 +7751,24 @@
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -7725,34 +7781,30 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr"/>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>08:00采样：该车到重点站巨峰路成园路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数42分钟，约±6分钟</t>
-        </is>
-      </c>
-      <c r="N60" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：08:18采样，终点ETA 10分钟</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7766,7 +7818,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7781,7 +7833,7 @@
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
@@ -7791,22 +7843,22 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -7819,24 +7871,24 @@
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A58633D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>07:20</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -7844,39 +7896,39 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr"/>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>08:00采样：该车到重点站巨峰路成园路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7890,7 +7942,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7900,12 +7952,12 @@
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
@@ -7915,22 +7967,22 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -7943,7 +7995,7 @@
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -7953,7 +8005,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -7973,34 +8025,34 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr"/>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>08:00采样：该车到重点站金高路俱进路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±5分钟</t>
+          <t>08:18采样：该车到重点站云山路灵山路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数15分钟，约±6分钟</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -8014,7 +8066,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -8049,12 +8101,12 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -8067,7 +8119,7 @@
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -8077,7 +8129,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -8097,34 +8149,30 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr"/>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>08:00采样：该车到重点站巨峰路成园路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数42分钟，约±6分钟</t>
-        </is>
-      </c>
-      <c r="N63" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：08:18采样，终点ETA 19分钟</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8138,7 +8186,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -8153,7 +8201,7 @@
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
@@ -8163,22 +8211,22 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -8191,7 +8239,7 @@
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -8201,7 +8249,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -8221,30 +8269,34 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr"/>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N64" s="2" t="inlineStr"/>
+          <t>08:18采样：该车到重点站云山路灵山路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数13分钟，约±6分钟</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8258,7 +8310,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8268,17 +8320,17 @@
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
@@ -8288,13 +8340,17 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC64" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8307,7 +8363,7 @@
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -8317,7 +8373,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -8337,19 +8393,19 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr"/>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>08:00采样：该车到重点站金杨路枣庄路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±5分钟</t>
+          <t>08:18采样：该车到重点站杨高北路（外高桥保税区南站） ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数29分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -8359,12 +8415,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8378,7 +8434,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8413,12 +8469,12 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -8431,7 +8487,7 @@
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -8441,7 +8497,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -8461,19 +8517,19 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr"/>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>08:00采样：该车到重点站杨高北路夏碧路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±5分钟</t>
+          <t>08:18采样：该车到重点站张杨北路博兴路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数30分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -8483,12 +8539,12 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8502,7 +8558,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8537,12 +8593,12 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -8555,24 +8611,24 @@
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>08:03</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -8585,19 +8641,19 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr"/>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±5分钟</t>
+          <t>08:18采样：该车到重点站五莲路归昌路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -8607,12 +8663,12 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8626,7 +8682,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8641,7 +8697,7 @@
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
@@ -8651,22 +8707,22 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8679,24 +8735,24 @@
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A57902D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -8709,22 +8765,26 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr"/>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N68" s="2" t="inlineStr"/>
+          <t>08:18采样：该车到重点站杨高北路（外高桥保税区南站） ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数23分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -8732,7 +8792,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8746,7 +8806,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8756,17 +8816,17 @@
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
@@ -8776,13 +8836,17 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC68" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -8795,24 +8859,24 @@
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A53629D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -8825,34 +8889,30 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr"/>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N69" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8866,7 +8926,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8876,37 +8936,33 @@
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC69" s="2" t="inlineStr">
-        <is>
-          <t>95.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr"/>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -8919,24 +8975,24 @@
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -8949,34 +9005,34 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr"/>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数89分钟估算，约±6分钟</t>
+          <t>08:18采样：该车到重点站五莲路凌河路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数53分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8990,7 +9046,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -9005,7 +9061,7 @@
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
@@ -9015,22 +9071,22 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -9043,24 +9099,24 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>08:21</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -9073,30 +9129,34 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr"/>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N71" s="2" t="inlineStr"/>
+          <t>08:00采样：该车到重点站杨高北路夏碧路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9110,7 +9170,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -9120,17 +9180,17 @@
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
@@ -9140,13 +9200,17 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC71" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -9159,24 +9223,24 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A58633D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -9189,19 +9253,19 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr"/>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±5分钟</t>
+          <t>08:18采样：该车到重点站金高路行泰路 ETA 33分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -9211,12 +9275,12 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -9230,47 +9294,1023 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>95.5</t>
+        </is>
+      </c>
+      <c r="AD72" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr"/>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr"/>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr"/>
+      <c r="AD73" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr"/>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>08:18采样：该车到重点站云山路灵山路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="AD74" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr"/>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>89分钟</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数89分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AD75" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr"/>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AD76" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr"/>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
           <t>08:30</t>
         </is>
       </c>
-      <c r="W72" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X72" s="2" t="inlineStr">
+      <c r="X77" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="Y72" s="2" t="inlineStr">
+      <c r="Y77" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Z72" s="2" t="inlineStr">
+      <c r="Z77" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="AA72" s="2" t="inlineStr">
+      <c r="AA77" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB72" s="2" t="inlineStr">
+      <c r="AB77" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AC72" s="2" t="inlineStr">
-        <is>
-          <t>86.5</t>
-        </is>
-      </c>
-      <c r="AD72" s="2" t="inlineStr">
-        <is>
-          <t>4/18</t>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AD77" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr"/>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr"/>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr"/>
+      <c r="AD78" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr"/>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AD79" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr"/>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>79分钟</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr"/>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>88.5</t>
+        </is>
+      </c>
+      <c r="AD80" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-20-operations.xlsx
+++ b/data/export/2026-09-20-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD306"/>
+  <dimension ref="A1:AD308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -452,7 +452,7 @@
     <col width="20" customWidth="1" min="20" max="20"/>
     <col width="36" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="20" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
     <col width="22" customWidth="1" min="25" max="25"/>
     <col width="14" customWidth="1" min="26" max="26"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -729,12 +729,12 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1273,19 +1273,19 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>同车下一次反向发车09:10，减去该车自身同类时段历史终点停站中位数13分钟，约±12分钟</t>
+          <t>同车下一次反向发车09:10，减去该车自身同类时段历史终点停站中位数12分钟，约±12分钟</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1473,12 +1473,12 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2336,17 +2336,17 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3209,12 +3209,12 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3462,7 +3462,7 @@
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3532,7 +3532,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3581,7 +3581,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD26" s="2" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -4028,7 +4028,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -4072,17 +4072,17 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4698,7 +4698,7 @@
       </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4941,12 +4941,12 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AD38" s="2" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5313,7 +5313,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD39" s="2" t="inlineStr">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5437,12 +5437,12 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -5512,7 +5512,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5556,17 +5556,17 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5636,7 +5636,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -6132,7 +6132,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -6256,7 +6256,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6305,7 +6305,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AD47" s="2" t="inlineStr">
@@ -6504,7 +6504,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6548,17 +6548,17 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -7054,7 +7054,7 @@
       </c>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD56" s="2" t="inlineStr">
@@ -7620,7 +7620,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7669,12 +7669,12 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -7798,7 +7798,7 @@
       </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -7922,7 +7922,7 @@
       </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -7992,7 +7992,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -8240,7 +8240,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -8364,7 +8364,7 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD64" s="2" t="inlineStr">
@@ -8608,7 +8608,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8657,7 +8657,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AD66" s="2" t="inlineStr">
@@ -8732,7 +8732,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -8856,7 +8856,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8900,17 +8900,17 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -9034,7 +9034,7 @@
       </c>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -9352,7 +9352,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -9600,7 +9600,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9649,12 +9649,12 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -9778,7 +9778,7 @@
       </c>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -9902,7 +9902,7 @@
       </c>
       <c r="AD76" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -10220,7 +10220,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10269,7 +10269,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AD79" s="2" t="inlineStr">
@@ -10344,7 +10344,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10388,17 +10388,17 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AD80" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -10517,7 +10517,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD81" s="2" t="inlineStr">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -10889,12 +10889,12 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AD84" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -11088,7 +11088,7 @@
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -11266,7 +11266,7 @@
       </c>
       <c r="AD87" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -11390,7 +11390,7 @@
       </c>
       <c r="AD88" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -11460,7 +11460,7 @@
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -11509,12 +11509,12 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD89" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -11681,24 +11681,24 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>20:44</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr"/>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
@@ -11708,7 +11708,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AD91" s="2" t="inlineStr">
@@ -11800,27 +11800,31 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>20:44</t>
+          <t>20:46</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr"/>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：20:21采样，终点ETA 23分钟</t>
-        </is>
-      </c>
-      <c r="N92" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11828,7 +11832,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11852,12 +11856,12 @@
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
@@ -11877,7 +11881,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD92" s="2" t="inlineStr">
@@ -11920,29 +11924,29 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:03</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr"/>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站唐陆公路龙东大道 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数31分钟，约±6分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
@@ -11952,7 +11956,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -11976,12 +11980,12 @@
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
@@ -12001,12 +12005,12 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AD93" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -12044,7 +12048,7 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
@@ -12054,17 +12058,21 @@
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr"/>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：20:21采样，终点ETA 47分钟</t>
-        </is>
-      </c>
-      <c r="N94" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -12072,7 +12080,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -12096,17 +12104,17 @@
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA94" s="2" t="inlineStr">
@@ -12116,17 +12124,17 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AD94" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -12164,7 +12172,7 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
@@ -12181,12 +12189,12 @@
       <c r="L95" s="2" t="inlineStr"/>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站博兴路东陆路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数53分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
@@ -12196,7 +12204,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12220,12 +12228,12 @@
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -12288,29 +12296,29 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>21:47</t>
+          <t>21:43</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr"/>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数77分钟估算，约±8分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr">
@@ -12320,7 +12328,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12344,12 +12352,12 @@
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
@@ -12369,12 +12377,12 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD96" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -12417,26 +12425,22 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>22:05</t>
+          <t>22:01</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr"/>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数75分钟估算，约±10分钟</t>
-        </is>
-      </c>
-      <c r="N97" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：21:22采样，终点ETA 39分钟</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr"/>
       <c r="O97" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -12444,7 +12448,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12468,12 +12472,12 @@
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -12493,7 +12497,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AD97" s="2" t="inlineStr">
@@ -12541,24 +12545,24 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>22:28</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr"/>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±10分钟</t>
+          <t>21:22采样：该车到重点站长岛路台儿庄路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数71分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O98" s="2" t="inlineStr">
@@ -12568,7 +12572,7 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -12597,7 +12601,7 @@
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
@@ -12612,17 +12616,17 @@
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AD98" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -12816,7 +12820,7 @@
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
@@ -12865,12 +12869,12 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AD100" s="2" t="inlineStr">
         <is>
-          <t>13/32</t>
+          <t>14/32</t>
         </is>
       </c>
     </row>
@@ -12994,7 +12998,7 @@
       </c>
       <c r="AD101" s="2" t="inlineStr">
         <is>
-          <t>6/32</t>
+          <t>7/32</t>
         </is>
       </c>
     </row>
@@ -13118,7 +13122,7 @@
       </c>
       <c r="AD102" s="2" t="inlineStr">
         <is>
-          <t>10/32</t>
+          <t>11/32</t>
         </is>
       </c>
     </row>
@@ -13320,7 +13324,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -13369,12 +13373,12 @@
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AD104" s="2" t="inlineStr">
         <is>
-          <t>7/32</t>
+          <t>5/32</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13618,7 @@
       </c>
       <c r="AD106" s="2" t="inlineStr">
         <is>
-          <t>20/32</t>
+          <t>19/32</t>
         </is>
       </c>
     </row>
@@ -13738,7 +13742,7 @@
       </c>
       <c r="AD107" s="2" t="inlineStr">
         <is>
-          <t>15/32</t>
+          <t>17/32</t>
         </is>
       </c>
     </row>
@@ -13808,7 +13812,7 @@
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -13857,12 +13861,12 @@
       </c>
       <c r="AC108" s="2" t="inlineStr">
         <is>
-          <t>136.8</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AD108" s="2" t="inlineStr">
         <is>
-          <t>16/32</t>
+          <t>12/32</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13936,7 @@
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
@@ -13981,12 +13985,12 @@
       </c>
       <c r="AC109" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AD109" s="2" t="inlineStr">
         <is>
-          <t>23/32</t>
+          <t>20/32</t>
         </is>
       </c>
     </row>
@@ -14180,7 +14184,7 @@
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -14229,12 +14233,12 @@
       </c>
       <c r="AC111" s="2" t="inlineStr">
         <is>
-          <t>135.8</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AD111" s="2" t="inlineStr">
         <is>
-          <t>12/32</t>
+          <t>15/32</t>
         </is>
       </c>
     </row>
@@ -14354,7 +14358,7 @@
       </c>
       <c r="AD112" s="2" t="inlineStr">
         <is>
-          <t>11/32</t>
+          <t>13/32</t>
         </is>
       </c>
     </row>
@@ -14490,7 +14494,7 @@
       </c>
       <c r="AD113" s="2" t="inlineStr">
         <is>
-          <t>13/32</t>
+          <t>15/32</t>
         </is>
       </c>
     </row>
@@ -14560,7 +14564,7 @@
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q114" s="2" t="inlineStr">
@@ -14604,17 +14608,17 @@
       </c>
       <c r="AB114" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC114" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AD114" s="2" t="inlineStr">
         <is>
-          <t>22/32</t>
+          <t>7/32</t>
         </is>
       </c>
     </row>
@@ -14684,7 +14688,7 @@
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q115" s="2" t="inlineStr">
@@ -14733,12 +14737,12 @@
       </c>
       <c r="AC115" s="2" t="inlineStr">
         <is>
-          <t>140.8</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AD115" s="2" t="inlineStr">
         <is>
-          <t>24/32</t>
+          <t>25/32</t>
         </is>
       </c>
     </row>
@@ -14862,7 +14866,7 @@
       </c>
       <c r="AD116" s="2" t="inlineStr">
         <is>
-          <t>7/32</t>
+          <t>9/32</t>
         </is>
       </c>
     </row>
@@ -14932,7 +14936,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -14981,12 +14985,12 @@
       </c>
       <c r="AC117" s="2" t="inlineStr">
         <is>
-          <t>141.2</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AD117" s="2" t="inlineStr">
         <is>
-          <t>26/32</t>
+          <t>23/32</t>
         </is>
       </c>
     </row>
@@ -15176,7 +15180,7 @@
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
@@ -15220,17 +15224,17 @@
       </c>
       <c r="AB119" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC119" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AD119" s="2" t="inlineStr">
         <is>
-          <t>3/32</t>
+          <t>2/32</t>
         </is>
       </c>
     </row>
@@ -15424,7 +15428,7 @@
       </c>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q121" s="2" t="inlineStr">
@@ -15548,7 +15552,7 @@
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
@@ -15592,17 +15596,17 @@
       </c>
       <c r="AB122" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC122" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AD122" s="2" t="inlineStr">
         <is>
-          <t>17/32</t>
+          <t>22/32</t>
         </is>
       </c>
     </row>
@@ -15796,7 +15800,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
@@ -15845,12 +15849,12 @@
       </c>
       <c r="AC124" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AD124" s="2" t="inlineStr">
         <is>
-          <t>19/32</t>
+          <t>18/32</t>
         </is>
       </c>
     </row>
@@ -15974,7 +15978,7 @@
       </c>
       <c r="AD125" s="2" t="inlineStr">
         <is>
-          <t>9/32</t>
+          <t>10/32</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16048,7 @@
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
@@ -16088,17 +16092,17 @@
       </c>
       <c r="AB126" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC126" s="2" t="inlineStr">
         <is>
-          <t>130.2</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AD126" s="2" t="inlineStr">
         <is>
-          <t>2/32</t>
+          <t>3/32</t>
         </is>
       </c>
     </row>
@@ -16292,7 +16296,7 @@
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q128" s="2" t="inlineStr">
@@ -16341,12 +16345,12 @@
       </c>
       <c r="AC128" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AD128" s="2" t="inlineStr">
         <is>
-          <t>13/32</t>
+          <t>14/32</t>
         </is>
       </c>
     </row>
@@ -16470,7 +16474,7 @@
       </c>
       <c r="AD129" s="2" t="inlineStr">
         <is>
-          <t>6/32</t>
+          <t>7/32</t>
         </is>
       </c>
     </row>
@@ -16594,7 +16598,7 @@
       </c>
       <c r="AD130" s="2" t="inlineStr">
         <is>
-          <t>10/32</t>
+          <t>11/32</t>
         </is>
       </c>
     </row>
@@ -16796,7 +16800,7 @@
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
@@ -16845,12 +16849,12 @@
       </c>
       <c r="AC132" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AD132" s="2" t="inlineStr">
         <is>
-          <t>7/32</t>
+          <t>5/32</t>
         </is>
       </c>
     </row>
@@ -17090,7 +17094,7 @@
       </c>
       <c r="AD134" s="2" t="inlineStr">
         <is>
-          <t>20/32</t>
+          <t>19/32</t>
         </is>
       </c>
     </row>
@@ -17214,7 +17218,7 @@
       </c>
       <c r="AD135" s="2" t="inlineStr">
         <is>
-          <t>15/32</t>
+          <t>17/32</t>
         </is>
       </c>
     </row>
@@ -17284,7 +17288,7 @@
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q136" s="2" t="inlineStr">
@@ -17333,12 +17337,12 @@
       </c>
       <c r="AC136" s="2" t="inlineStr">
         <is>
-          <t>136.8</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AD136" s="2" t="inlineStr">
         <is>
-          <t>16/32</t>
+          <t>12/32</t>
         </is>
       </c>
     </row>
@@ -17408,7 +17412,7 @@
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q137" s="2" t="inlineStr">
@@ -17457,12 +17461,12 @@
       </c>
       <c r="AC137" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AD137" s="2" t="inlineStr">
         <is>
-          <t>23/32</t>
+          <t>20/32</t>
         </is>
       </c>
     </row>
@@ -17528,7 +17532,7 @@
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q138" s="2" t="inlineStr">
@@ -17577,12 +17581,12 @@
       </c>
       <c r="AC138" s="2" t="inlineStr">
         <is>
-          <t>135.8</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AD138" s="2" t="inlineStr">
         <is>
-          <t>12/32</t>
+          <t>15/32</t>
         </is>
       </c>
     </row>
@@ -17706,7 +17710,7 @@
       </c>
       <c r="AD139" s="2" t="inlineStr">
         <is>
-          <t>11/32</t>
+          <t>13/32</t>
         </is>
       </c>
     </row>
@@ -17772,7 +17776,7 @@
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q140" s="2" t="inlineStr">
@@ -17821,12 +17825,12 @@
       </c>
       <c r="AC140" s="2" t="inlineStr">
         <is>
-          <t>140.8</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AD140" s="2" t="inlineStr">
         <is>
-          <t>24/32</t>
+          <t>25/32</t>
         </is>
       </c>
     </row>
@@ -17896,7 +17900,7 @@
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q141" s="2" t="inlineStr">
@@ -17940,17 +17944,17 @@
       </c>
       <c r="AB141" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC141" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AD141" s="2" t="inlineStr">
         <is>
-          <t>22/32</t>
+          <t>7/32</t>
         </is>
       </c>
     </row>
@@ -17993,12 +17997,12 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr"/>
@@ -18020,7 +18024,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q142" s="2" t="inlineStr">
@@ -18069,12 +18073,12 @@
       </c>
       <c r="AC142" s="2" t="inlineStr">
         <is>
-          <t>141.2</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AD142" s="2" t="inlineStr">
         <is>
-          <t>26/32</t>
+          <t>23/32</t>
         </is>
       </c>
     </row>
@@ -18198,7 +18202,7 @@
       </c>
       <c r="AD143" s="2" t="inlineStr">
         <is>
-          <t>7/32</t>
+          <t>9/32</t>
         </is>
       </c>
     </row>
@@ -18388,7 +18392,7 @@
       </c>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q145" s="2" t="inlineStr">
@@ -18432,17 +18436,17 @@
       </c>
       <c r="AB145" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC145" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AD145" s="2" t="inlineStr">
         <is>
-          <t>3/32</t>
+          <t>2/32</t>
         </is>
       </c>
     </row>
@@ -18632,7 +18636,7 @@
       </c>
       <c r="P147" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q147" s="2" t="inlineStr">
@@ -18676,17 +18680,17 @@
       </c>
       <c r="AB147" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC147" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AD147" s="2" t="inlineStr">
         <is>
-          <t>17/32</t>
+          <t>22/32</t>
         </is>
       </c>
     </row>
@@ -18810,7 +18814,7 @@
       </c>
       <c r="AD148" s="2" t="inlineStr">
         <is>
-          <t>9/32</t>
+          <t>10/32</t>
         </is>
       </c>
     </row>
@@ -18880,7 +18884,7 @@
       </c>
       <c r="P149" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q149" s="2" t="inlineStr">
@@ -18924,17 +18928,17 @@
       </c>
       <c r="AB149" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC149" s="2" t="inlineStr">
         <is>
-          <t>130.2</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AD149" s="2" t="inlineStr">
         <is>
-          <t>2/32</t>
+          <t>3/32</t>
         </is>
       </c>
     </row>
@@ -19058,7 +19062,7 @@
       </c>
       <c r="AD150" s="2" t="inlineStr">
         <is>
-          <t>10/32</t>
+          <t>11/32</t>
         </is>
       </c>
     </row>
@@ -19182,7 +19186,7 @@
       </c>
       <c r="AD151" s="2" t="inlineStr">
         <is>
-          <t>6/32</t>
+          <t>7/32</t>
         </is>
       </c>
     </row>
@@ -19306,7 +19310,7 @@
       </c>
       <c r="AD152" s="2" t="inlineStr">
         <is>
-          <t>15/32</t>
+          <t>17/32</t>
         </is>
       </c>
     </row>
@@ -19430,7 +19434,7 @@
       </c>
       <c r="AD153" s="2" t="inlineStr">
         <is>
-          <t>20/32</t>
+          <t>19/32</t>
         </is>
       </c>
     </row>
@@ -19496,7 +19500,7 @@
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q154" s="2" t="inlineStr">
@@ -19806,7 +19810,7 @@
       </c>
       <c r="AD156" s="2" t="inlineStr">
         <is>
-          <t>11/32</t>
+          <t>13/32</t>
         </is>
       </c>
     </row>
@@ -19930,7 +19934,7 @@
       </c>
       <c r="AD157" s="2" t="inlineStr">
         <is>
-          <t>13/32</t>
+          <t>15/32</t>
         </is>
       </c>
     </row>
@@ -19996,7 +20000,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q158" s="2" t="inlineStr">
@@ -20045,12 +20049,12 @@
       </c>
       <c r="AC158" s="2" t="inlineStr">
         <is>
-          <t>140.8</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AD158" s="2" t="inlineStr">
         <is>
-          <t>24/32</t>
+          <t>25/32</t>
         </is>
       </c>
     </row>
@@ -20174,7 +20178,7 @@
       </c>
       <c r="AD159" s="2" t="inlineStr">
         <is>
-          <t>7/32</t>
+          <t>9/32</t>
         </is>
       </c>
     </row>
@@ -20546,7 +20550,7 @@
       </c>
       <c r="AD162" s="2" t="inlineStr">
         <is>
-          <t>9/32</t>
+          <t>10/32</t>
         </is>
       </c>
     </row>
@@ -20794,7 +20798,7 @@
       </c>
       <c r="AD164" s="2" t="inlineStr">
         <is>
-          <t>10/32</t>
+          <t>11/32</t>
         </is>
       </c>
     </row>
@@ -21158,7 +21162,7 @@
       </c>
       <c r="AD167" s="2" t="inlineStr">
         <is>
-          <t>15/32</t>
+          <t>17/32</t>
         </is>
       </c>
     </row>
@@ -21224,7 +21228,7 @@
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q168" s="2" t="inlineStr">
@@ -21273,12 +21277,12 @@
       </c>
       <c r="AC168" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AD168" s="2" t="inlineStr">
         <is>
-          <t>23/32</t>
+          <t>20/32</t>
         </is>
       </c>
     </row>
@@ -21600,7 +21604,7 @@
       </c>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q171" s="2" t="inlineStr">
@@ -21649,12 +21653,12 @@
       </c>
       <c r="AC171" s="2" t="inlineStr">
         <is>
-          <t>135.8</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AD171" s="2" t="inlineStr">
         <is>
-          <t>12/32</t>
+          <t>15/32</t>
         </is>
       </c>
     </row>
@@ -21724,7 +21728,7 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q172" s="2" t="inlineStr">
@@ -21848,7 +21852,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q173" s="2" t="inlineStr">
@@ -21897,12 +21901,12 @@
       </c>
       <c r="AC173" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AD173" s="2" t="inlineStr">
         <is>
-          <t>19/32</t>
+          <t>18/32</t>
         </is>
       </c>
     </row>
@@ -21968,7 +21972,7 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -22017,12 +22021,12 @@
       </c>
       <c r="AC174" s="2" t="inlineStr">
         <is>
-          <t>141.2</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AD174" s="2" t="inlineStr">
         <is>
-          <t>26/32</t>
+          <t>23/32</t>
         </is>
       </c>
     </row>
@@ -22092,7 +22096,7 @@
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q175" s="2" t="inlineStr">
@@ -22216,7 +22220,7 @@
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q176" s="2" t="inlineStr">
@@ -22265,12 +22269,12 @@
       </c>
       <c r="AC176" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AD176" s="2" t="inlineStr">
         <is>
-          <t>17/32</t>
+          <t>23/32</t>
         </is>
       </c>
     </row>
@@ -22340,7 +22344,7 @@
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q177" s="2" t="inlineStr">
@@ -22384,17 +22388,17 @@
       </c>
       <c r="AB177" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC177" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AD177" s="2" t="inlineStr">
         <is>
-          <t>17/32</t>
+          <t>22/32</t>
         </is>
       </c>
     </row>
@@ -22460,7 +22464,7 @@
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q178" s="2" t="inlineStr">
@@ -22504,17 +22508,17 @@
       </c>
       <c r="AB178" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC178" s="2" t="inlineStr">
         <is>
-          <t>130.2</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AD178" s="2" t="inlineStr">
         <is>
-          <t>2/32</t>
+          <t>3/32</t>
         </is>
       </c>
     </row>
@@ -22584,7 +22588,7 @@
       </c>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q179" s="2" t="inlineStr">
@@ -22633,12 +22637,12 @@
       </c>
       <c r="AC179" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AD179" s="2" t="inlineStr">
         <is>
-          <t>13/32</t>
+          <t>14/32</t>
         </is>
       </c>
     </row>
@@ -22708,7 +22712,7 @@
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q180" s="2" t="inlineStr">
@@ -22757,12 +22761,12 @@
       </c>
       <c r="AC180" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AD180" s="2" t="inlineStr">
         <is>
-          <t>7/32</t>
+          <t>5/32</t>
         </is>
       </c>
     </row>
@@ -22882,7 +22886,7 @@
       </c>
       <c r="AD181" s="2" t="inlineStr">
         <is>
-          <t>6/32</t>
+          <t>7/32</t>
         </is>
       </c>
     </row>
@@ -22952,7 +22956,7 @@
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q182" s="2" t="inlineStr">
@@ -23001,12 +23005,12 @@
       </c>
       <c r="AC182" s="2" t="inlineStr">
         <is>
-          <t>136.8</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AD182" s="2" t="inlineStr">
         <is>
-          <t>16/32</t>
+          <t>12/32</t>
         </is>
       </c>
     </row>
@@ -23130,7 +23134,7 @@
       </c>
       <c r="AD183" s="2" t="inlineStr">
         <is>
-          <t>20/32</t>
+          <t>19/32</t>
         </is>
       </c>
     </row>
@@ -23378,7 +23382,7 @@
       </c>
       <c r="AD185" s="2" t="inlineStr">
         <is>
-          <t>11/32</t>
+          <t>13/32</t>
         </is>
       </c>
     </row>
@@ -23448,7 +23452,7 @@
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q186" s="2" t="inlineStr">
@@ -23492,17 +23496,17 @@
       </c>
       <c r="AB186" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC186" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AD186" s="2" t="inlineStr">
         <is>
-          <t>22/32</t>
+          <t>7/32</t>
         </is>
       </c>
     </row>
@@ -23626,7 +23630,7 @@
       </c>
       <c r="AD187" s="2" t="inlineStr">
         <is>
-          <t>7/32</t>
+          <t>9/32</t>
         </is>
       </c>
     </row>
@@ -24184,7 +24188,7 @@
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q192" s="2" t="inlineStr">
@@ -24228,17 +24232,17 @@
       </c>
       <c r="AB192" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC192" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AD192" s="2" t="inlineStr">
         <is>
-          <t>3/32</t>
+          <t>2/32</t>
         </is>
       </c>
     </row>
@@ -24308,7 +24312,7 @@
       </c>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q193" s="2" t="inlineStr">
@@ -24400,29 +24404,29 @@
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="K194" s="2" t="inlineStr"/>
       <c r="L194" s="2" t="inlineStr"/>
       <c r="M194" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站康沈路秀沿路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数28分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N194" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O194" s="2" t="inlineStr">
@@ -24432,7 +24436,7 @@
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q194" s="2" t="inlineStr">
@@ -24456,12 +24460,12 @@
       </c>
       <c r="X194" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y194" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z194" s="2" t="inlineStr">
@@ -24481,12 +24485,12 @@
       </c>
       <c r="AC194" s="2" t="inlineStr">
         <is>
-          <t>140.8</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AD194" s="2" t="inlineStr">
         <is>
-          <t>24/32</t>
+          <t>25/32</t>
         </is>
       </c>
     </row>
@@ -24524,27 +24528,31 @@
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I195" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="J195" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="K195" s="2" t="inlineStr"/>
       <c r="L195" s="2" t="inlineStr"/>
       <c r="M195" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：20:21采样，终点ETA 40分钟</t>
-        </is>
-      </c>
-      <c r="N195" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N195" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O195" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -24552,7 +24560,7 @@
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q195" s="2" t="inlineStr">
@@ -24576,12 +24584,12 @@
       </c>
       <c r="X195" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y195" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z195" s="2" t="inlineStr">
@@ -24601,12 +24609,12 @@
       </c>
       <c r="AC195" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AD195" s="2" t="inlineStr">
         <is>
-          <t>19/32</t>
+          <t>18/32</t>
         </is>
       </c>
     </row>
@@ -24644,29 +24652,29 @@
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:09</t>
         </is>
       </c>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="K196" s="2" t="inlineStr"/>
       <c r="L196" s="2" t="inlineStr"/>
       <c r="M196" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站沪南路北中路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数53分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N196" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O196" s="2" t="inlineStr">
@@ -24676,7 +24684,7 @@
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q196" s="2" t="inlineStr">
@@ -24700,12 +24708,12 @@
       </c>
       <c r="X196" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y196" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z196" s="2" t="inlineStr">
@@ -24725,12 +24733,12 @@
       </c>
       <c r="AC196" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AD196" s="2" t="inlineStr">
         <is>
-          <t>23/32</t>
+          <t>20/32</t>
         </is>
       </c>
     </row>
@@ -24763,36 +24771,32 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq29推进至seq64，推进35站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I197" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J197" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K197" s="2" t="inlineStr"/>
       <c r="L197" s="2" t="inlineStr"/>
       <c r="M197" s="2" t="inlineStr">
         <is>
-          <t>20:01采样：该车到重点站丁香路锦绣路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数80分钟，约±12分钟</t>
-        </is>
-      </c>
-      <c r="N197" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N197" s="2" t="inlineStr"/>
       <c r="O197" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -24800,7 +24804,7 @@
       </c>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q197" s="2" t="inlineStr">
@@ -24808,10 +24812,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R197" s="2" t="inlineStr"/>
-      <c r="S197" s="2" t="inlineStr"/>
-      <c r="T197" s="2" t="inlineStr"/>
-      <c r="U197" s="2" t="inlineStr"/>
+      <c r="R197" s="2" t="inlineStr">
+        <is>
+          <t>物理seq28（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S197" s="2" t="inlineStr">
+        <is>
+          <t>20:02</t>
+        </is>
+      </c>
+      <c r="T197" s="2" t="inlineStr">
+        <is>
+          <t>20:11</t>
+        </is>
+      </c>
+      <c r="U197" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq28映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置锦绣路花木路 ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V197" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -24824,17 +24844,17 @@
       </c>
       <c r="X197" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y197" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z197" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA197" s="2" t="inlineStr">
@@ -24844,17 +24864,17 @@
       </c>
       <c r="AB197" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC197" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AD197" s="2" t="inlineStr">
         <is>
-          <t>17/32</t>
+          <t>22/32</t>
         </is>
       </c>
     </row>
@@ -24892,29 +24912,29 @@
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I198" s="2" t="inlineStr">
         <is>
-          <t>21:23</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K198" s="2" t="inlineStr"/>
       <c r="L198" s="2" t="inlineStr"/>
       <c r="M198" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站锦绣路罗山路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N198" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O198" s="2" t="inlineStr">
@@ -24924,7 +24944,7 @@
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q198" s="2" t="inlineStr">
@@ -24948,12 +24968,12 @@
       </c>
       <c r="X198" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y198" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z198" s="2" t="inlineStr">
@@ -24973,12 +24993,12 @@
       </c>
       <c r="AC198" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AD198" s="2" t="inlineStr">
         <is>
-          <t>13/32</t>
+          <t>14/32</t>
         </is>
       </c>
     </row>
@@ -25016,29 +25036,29 @@
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>21:29</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="J199" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K199" s="2" t="inlineStr"/>
       <c r="L199" s="2" t="inlineStr"/>
       <c r="M199" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站浦建路锦绣路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="N199" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O199" s="2" t="inlineStr">
@@ -25048,7 +25068,7 @@
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q199" s="2" t="inlineStr">
@@ -25072,12 +25092,12 @@
       </c>
       <c r="X199" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y199" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z199" s="2" t="inlineStr">
@@ -25097,12 +25117,12 @@
       </c>
       <c r="AC199" s="2" t="inlineStr">
         <is>
-          <t>135.8</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AD199" s="2" t="inlineStr">
         <is>
-          <t>12/32</t>
+          <t>15/32</t>
         </is>
       </c>
     </row>
@@ -25145,19 +25165,19 @@
       </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>21:38</t>
+          <t>21:43</t>
         </is>
       </c>
       <c r="J200" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="K200" s="2" t="inlineStr"/>
       <c r="L200" s="2" t="inlineStr"/>
       <c r="M200" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站沪南路高科西路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数74分钟，约±5分钟</t>
+          <t>20:51采样：该车到重点站云山路碧云路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N200" s="2" t="inlineStr">
@@ -25172,7 +25192,7 @@
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q200" s="2" t="inlineStr">
@@ -25221,12 +25241,12 @@
       </c>
       <c r="AC200" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AD200" s="2" t="inlineStr">
         <is>
-          <t>17/32</t>
+          <t>23/32</t>
         </is>
       </c>
     </row>
@@ -25259,36 +25279,32 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq55，推进27站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I201" s="2" t="inlineStr">
         <is>
-          <t>21:38</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J201" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K201" s="2" t="inlineStr"/>
       <c r="L201" s="2" t="inlineStr"/>
       <c r="M201" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站迎春路长柳路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数72分钟，约±8分钟</t>
-        </is>
-      </c>
-      <c r="N201" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N201" s="2" t="inlineStr"/>
       <c r="O201" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -25296,7 +25312,7 @@
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q201" s="2" t="inlineStr">
@@ -25304,10 +25320,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R201" s="2" t="inlineStr"/>
-      <c r="S201" s="2" t="inlineStr"/>
-      <c r="T201" s="2" t="inlineStr"/>
-      <c r="U201" s="2" t="inlineStr"/>
+      <c r="R201" s="2" t="inlineStr">
+        <is>
+          <t>丁香路锦绣路</t>
+        </is>
+      </c>
+      <c r="S201" s="2" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="T201" s="2" t="inlineStr">
+        <is>
+          <t>20:28</t>
+        </is>
+      </c>
+      <c r="U201" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq29映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±3分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V201" s="2" t="inlineStr">
         <is>
           <t>19:30</t>
@@ -25320,17 +25352,17 @@
       </c>
       <c r="X201" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y201" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z201" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA201" s="2" t="inlineStr">
@@ -25340,17 +25372,17 @@
       </c>
       <c r="AB201" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC201" s="2" t="inlineStr">
         <is>
-          <t>130.2</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AD201" s="2" t="inlineStr">
         <is>
-          <t>2/32</t>
+          <t>3/32</t>
         </is>
       </c>
     </row>
@@ -25393,19 +25425,19 @@
       </c>
       <c r="I202" s="2" t="inlineStr">
         <is>
-          <t>21:44</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="J202" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>121分钟</t>
         </is>
       </c>
       <c r="K202" s="2" t="inlineStr"/>
       <c r="L202" s="2" t="inlineStr"/>
       <c r="M202" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站沪南路高科西路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数79分钟，约±5分钟</t>
+          <t>21:20采样：该车到重点站东波路莱阳路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数16分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N202" s="2" t="inlineStr">
@@ -25420,7 +25452,7 @@
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q202" s="2" t="inlineStr">
@@ -25469,12 +25501,12 @@
       </c>
       <c r="AC202" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AD202" s="2" t="inlineStr">
         <is>
-          <t>7/32</t>
+          <t>5/32</t>
         </is>
       </c>
     </row>
@@ -25512,29 +25544,29 @@
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I203" s="2" t="inlineStr">
         <is>
-          <t>21:49</t>
+          <t>21:48</t>
         </is>
       </c>
       <c r="J203" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K203" s="2" t="inlineStr"/>
       <c r="L203" s="2" t="inlineStr"/>
       <c r="M203" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站白桦路明月路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数83分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N203" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O203" s="2" t="inlineStr">
@@ -25544,7 +25576,7 @@
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q203" s="2" t="inlineStr">
@@ -25568,12 +25600,12 @@
       </c>
       <c r="X203" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y203" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z203" s="2" t="inlineStr">
@@ -25593,12 +25625,12 @@
       </c>
       <c r="AC203" s="2" t="inlineStr">
         <is>
-          <t>141.2</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AD203" s="2" t="inlineStr">
         <is>
-          <t>26/32</t>
+          <t>23/32</t>
         </is>
       </c>
     </row>
@@ -25641,19 +25673,19 @@
       </c>
       <c r="I204" s="2" t="inlineStr">
         <is>
-          <t>22:08</t>
+          <t>22:04</t>
         </is>
       </c>
       <c r="J204" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="K204" s="2" t="inlineStr"/>
       <c r="L204" s="2" t="inlineStr"/>
       <c r="M204" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站博兴路兰城路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数106分钟，约±5分钟</t>
+          <t>21:20采样：该车到重点站沪南路御桥路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N204" s="2" t="inlineStr">
@@ -25668,7 +25700,7 @@
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q204" s="2" t="inlineStr">
@@ -25717,7 +25749,7 @@
       </c>
       <c r="AC204" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AD204" s="2" t="inlineStr">
@@ -25765,19 +25797,19 @@
       </c>
       <c r="I205" s="2" t="inlineStr">
         <is>
-          <t>22:15</t>
+          <t>22:06</t>
         </is>
       </c>
       <c r="J205" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="K205" s="2" t="inlineStr"/>
       <c r="L205" s="2" t="inlineStr"/>
       <c r="M205" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站川周公路康沈路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数112分钟，约±5分钟</t>
+          <t>21:20采样：该车到重点站云山路碧云路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数46分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N205" s="2" t="inlineStr">
@@ -25792,7 +25824,7 @@
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q205" s="2" t="inlineStr">
@@ -25841,12 +25873,12 @@
       </c>
       <c r="AC205" s="2" t="inlineStr">
         <is>
-          <t>136.8</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AD205" s="2" t="inlineStr">
         <is>
-          <t>16/32</t>
+          <t>12/32</t>
         </is>
       </c>
     </row>
@@ -25889,22 +25921,26 @@
       </c>
       <c r="I206" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:24</t>
         </is>
       </c>
       <c r="J206" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>115分钟</t>
         </is>
       </c>
       <c r="K206" s="2" t="inlineStr"/>
       <c r="L206" s="2" t="inlineStr"/>
       <c r="M206" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N206" s="2" t="inlineStr"/>
+          <t>21:20采样：该车到重点站锦绣路花木路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数61分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N206" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O206" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -25912,7 +25948,7 @@
       </c>
       <c r="P206" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q206" s="2" t="inlineStr">
@@ -25936,17 +25972,17 @@
       </c>
       <c r="X206" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y206" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z206" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA206" s="2" t="inlineStr">
@@ -25956,17 +25992,17 @@
       </c>
       <c r="AB206" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC206" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AD206" s="2" t="inlineStr">
         <is>
-          <t>22/32</t>
+          <t>7/32</t>
         </is>
       </c>
     </row>
@@ -26009,22 +26045,26 @@
       </c>
       <c r="I207" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:54</t>
         </is>
       </c>
       <c r="J207" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>120分钟</t>
         </is>
       </c>
       <c r="K207" s="2" t="inlineStr"/>
       <c r="L207" s="2" t="inlineStr"/>
       <c r="M207" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N207" s="2" t="inlineStr"/>
+          <t>21:20采样：该车到重点站康沈路秀康路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数94分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N207" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O207" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -26032,7 +26072,7 @@
       </c>
       <c r="P207" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q207" s="2" t="inlineStr">
@@ -26056,17 +26096,17 @@
       </c>
       <c r="X207" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y207" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z207" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA207" s="2" t="inlineStr">
@@ -26076,17 +26116,17 @@
       </c>
       <c r="AB207" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC207" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AD207" s="2" t="inlineStr">
         <is>
-          <t>3/32</t>
+          <t>2/32</t>
         </is>
       </c>
     </row>
@@ -26152,7 +26192,7 @@
       </c>
       <c r="P208" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q208" s="2" t="inlineStr">
@@ -26201,7 +26241,7 @@
       </c>
       <c r="AC208" s="2" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AD208" s="2" t="inlineStr">
@@ -26326,7 +26366,7 @@
       </c>
       <c r="AD209" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -26636,7 +26676,7 @@
       </c>
       <c r="P212" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q212" s="2" t="inlineStr">
@@ -26675,17 +26715,17 @@
       </c>
       <c r="AA212" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB212" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC212" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AD212" s="2" t="inlineStr">
@@ -26760,7 +26800,7 @@
       </c>
       <c r="P213" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q213" s="2" t="inlineStr">
@@ -26804,17 +26844,17 @@
       </c>
       <c r="AB213" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC213" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AD213" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -27062,7 +27102,7 @@
       </c>
       <c r="AD215" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -27132,7 +27172,7 @@
       </c>
       <c r="P216" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q216" s="2" t="inlineStr">
@@ -27176,17 +27216,17 @@
       </c>
       <c r="AB216" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC216" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AD216" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -27256,7 +27296,7 @@
       </c>
       <c r="P217" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q217" s="2" t="inlineStr">
@@ -27305,12 +27345,12 @@
       </c>
       <c r="AC217" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AD217" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -27628,7 +27668,7 @@
       </c>
       <c r="P220" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q220" s="2" t="inlineStr">
@@ -27667,17 +27707,17 @@
       </c>
       <c r="AA220" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB220" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC220" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AD220" s="2" t="inlineStr">
@@ -27926,7 +27966,7 @@
       </c>
       <c r="AD222" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -28050,7 +28090,7 @@
       </c>
       <c r="AD223" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -28120,7 +28160,7 @@
       </c>
       <c r="P224" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q224" s="2" t="inlineStr">
@@ -28169,7 +28209,7 @@
       </c>
       <c r="AC224" s="2" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AD224" s="2" t="inlineStr">
@@ -28414,7 +28454,7 @@
       </c>
       <c r="AD226" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -28732,7 +28772,7 @@
       </c>
       <c r="P229" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q229" s="2" t="inlineStr">
@@ -28776,17 +28816,17 @@
       </c>
       <c r="AB229" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC229" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AD229" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -29026,7 +29066,7 @@
       </c>
       <c r="AD231" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -29096,7 +29136,7 @@
       </c>
       <c r="P232" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q232" s="2" t="inlineStr">
@@ -29135,17 +29175,17 @@
       </c>
       <c r="AA232" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB232" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC232" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AD232" s="2" t="inlineStr">
@@ -29220,7 +29260,7 @@
       </c>
       <c r="P233" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q233" s="2" t="inlineStr">
@@ -29269,12 +29309,12 @@
       </c>
       <c r="AC233" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AD233" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -29468,7 +29508,7 @@
       </c>
       <c r="P235" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q235" s="2" t="inlineStr">
@@ -29507,17 +29547,17 @@
       </c>
       <c r="AA235" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB235" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC235" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AD235" s="2" t="inlineStr">
@@ -29592,7 +29632,7 @@
       </c>
       <c r="P236" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q236" s="2" t="inlineStr">
@@ -29636,17 +29676,17 @@
       </c>
       <c r="AB236" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC236" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AD236" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -29770,7 +29810,7 @@
       </c>
       <c r="AD237" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -30138,7 +30178,7 @@
       </c>
       <c r="AD240" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -30328,7 +30368,7 @@
       </c>
       <c r="P242" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q242" s="2" t="inlineStr">
@@ -30384,17 +30424,17 @@
       </c>
       <c r="AB242" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC242" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AD242" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -30642,7 +30682,7 @@
       </c>
       <c r="AD244" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -30832,7 +30872,7 @@
       </c>
       <c r="P246" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q246" s="2" t="inlineStr">
@@ -30893,12 +30933,12 @@
       </c>
       <c r="AC246" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AD246" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -30968,7 +31008,7 @@
       </c>
       <c r="P247" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q247" s="2" t="inlineStr">
@@ -31007,17 +31047,17 @@
       </c>
       <c r="AA247" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB247" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC247" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AD247" s="2" t="inlineStr">
@@ -31270,7 +31310,7 @@
       </c>
       <c r="AD249" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -31518,7 +31558,7 @@
       </c>
       <c r="AD251" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -31890,7 +31930,7 @@
       </c>
       <c r="AD254" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -32084,7 +32124,7 @@
       </c>
       <c r="P256" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q256" s="2" t="inlineStr">
@@ -32123,17 +32163,17 @@
       </c>
       <c r="AA256" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB256" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC256" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AD256" s="2" t="inlineStr">
@@ -32386,7 +32426,7 @@
       </c>
       <c r="AD258" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -32634,7 +32674,7 @@
       </c>
       <c r="AD260" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -32952,7 +32992,7 @@
       </c>
       <c r="P263" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q263" s="2" t="inlineStr">
@@ -33001,7 +33041,7 @@
       </c>
       <c r="AC263" s="2" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AD263" s="2" t="inlineStr">
@@ -33130,7 +33170,7 @@
       </c>
       <c r="AD264" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -33622,7 +33662,7 @@
       </c>
       <c r="AD268" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -33692,7 +33732,7 @@
       </c>
       <c r="P269" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q269" s="2" t="inlineStr">
@@ -33731,17 +33771,17 @@
       </c>
       <c r="AA269" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB269" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC269" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AD269" s="2" t="inlineStr">
@@ -33936,7 +33976,7 @@
       </c>
       <c r="P271" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q271" s="2" t="inlineStr">
@@ -33980,17 +34020,17 @@
       </c>
       <c r="AB271" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC271" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AD271" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -34060,7 +34100,7 @@
       </c>
       <c r="P272" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q272" s="2" t="inlineStr">
@@ -34104,17 +34144,17 @@
       </c>
       <c r="AB272" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC272" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AD272" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -34362,7 +34402,7 @@
       </c>
       <c r="AD274" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -34556,7 +34596,7 @@
       </c>
       <c r="P276" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q276" s="2" t="inlineStr">
@@ -34605,12 +34645,12 @@
       </c>
       <c r="AC276" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AD276" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -34854,7 +34894,7 @@
       </c>
       <c r="AD278" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -34924,7 +34964,7 @@
       </c>
       <c r="P279" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q279" s="2" t="inlineStr">
@@ -34973,7 +35013,7 @@
       </c>
       <c r="AC279" s="2" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AD279" s="2" t="inlineStr">
@@ -35346,7 +35386,7 @@
       </c>
       <c r="AD282" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -35660,7 +35700,7 @@
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q285" s="2" t="inlineStr">
@@ -35699,17 +35739,17 @@
       </c>
       <c r="AA285" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB285" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC285" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AD285" s="2" t="inlineStr">
@@ -35784,7 +35824,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q286" s="2" t="inlineStr">
@@ -35828,17 +35868,17 @@
       </c>
       <c r="AB286" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC286" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AD286" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -35908,7 +35948,7 @@
       </c>
       <c r="P287" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q287" s="2" t="inlineStr">
@@ -35947,17 +35987,17 @@
       </c>
       <c r="AA287" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB287" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC287" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AD287" s="2" t="inlineStr">
@@ -36156,7 +36196,7 @@
       </c>
       <c r="P289" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q289" s="2" t="inlineStr">
@@ -36200,17 +36240,17 @@
       </c>
       <c r="AB289" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC289" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AD289" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -36334,7 +36374,7 @@
       </c>
       <c r="AD290" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -36528,7 +36568,7 @@
       </c>
       <c r="P292" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q292" s="2" t="inlineStr">
@@ -36577,12 +36617,12 @@
       </c>
       <c r="AC292" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AD292" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -36706,7 +36746,7 @@
       </c>
       <c r="AD293" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -37024,7 +37064,7 @@
       </c>
       <c r="P296" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q296" s="2" t="inlineStr">
@@ -37073,7 +37113,7 @@
       </c>
       <c r="AC296" s="2" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AD296" s="2" t="inlineStr">
@@ -37369,24 +37409,24 @@
       </c>
       <c r="I299" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="J299" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K299" s="2" t="inlineStr"/>
       <c r="L299" s="2" t="inlineStr"/>
       <c r="M299" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="N299" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O299" s="2" t="inlineStr">
@@ -37396,7 +37436,7 @@
       </c>
       <c r="P299" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q299" s="2" t="inlineStr">
@@ -37435,17 +37475,17 @@
       </c>
       <c r="AA299" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB299" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC299" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AD299" s="2" t="inlineStr">
@@ -37493,12 +37533,12 @@
       </c>
       <c r="I300" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="J300" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K300" s="2" t="inlineStr"/>
@@ -37520,7 +37560,7 @@
       </c>
       <c r="P300" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q300" s="2" t="inlineStr">
@@ -37559,17 +37599,17 @@
       </c>
       <c r="AA300" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB300" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC300" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AD300" s="2" t="inlineStr">
@@ -37617,19 +37657,19 @@
       </c>
       <c r="I301" s="2" t="inlineStr">
         <is>
-          <t>21:18</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="J301" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K301" s="2" t="inlineStr"/>
       <c r="L301" s="2" t="inlineStr"/>
       <c r="M301" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：20:20采样，终点ETA 58分钟</t>
+          <t>SHMAAS末次终点ETA推算：20:50采样，终点ETA 18分钟</t>
         </is>
       </c>
       <c r="N301" s="2" t="inlineStr"/>
@@ -37640,7 +37680,7 @@
       </c>
       <c r="P301" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q301" s="2" t="inlineStr">
@@ -37664,17 +37704,17 @@
       </c>
       <c r="X301" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y301" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z301" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA301" s="2" t="inlineStr">
@@ -37684,17 +37724,17 @@
       </c>
       <c r="AB301" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC301" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AD301" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -37737,26 +37777,22 @@
       </c>
       <c r="I302" s="2" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="J302" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>113分钟</t>
         </is>
       </c>
       <c r="K302" s="2" t="inlineStr"/>
       <c r="L302" s="2" t="inlineStr"/>
       <c r="M302" s="2" t="inlineStr">
         <is>
-          <t>同车下一次反向发车21:40，减去该车自身同类时段历史终点停站中位数25分钟，约±15分钟</t>
-        </is>
-      </c>
-      <c r="N302" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：21:00采样，终点ETA 50分钟</t>
+        </is>
+      </c>
+      <c r="N302" s="2" t="inlineStr"/>
       <c r="O302" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -37764,7 +37800,7 @@
       </c>
       <c r="P302" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q302" s="2" t="inlineStr">
@@ -37788,17 +37824,17 @@
       </c>
       <c r="X302" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y302" s="2" t="inlineStr">
         <is>
-          <t>同车反向发车反推</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Z302" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA302" s="2" t="inlineStr">
@@ -37808,17 +37844,17 @@
       </c>
       <c r="AB302" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC302" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AD302" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -37856,24 +37892,24 @@
       </c>
       <c r="H303" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I303" s="2" t="inlineStr">
         <is>
-          <t>21:37</t>
+          <t>21:38</t>
         </is>
       </c>
       <c r="J303" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K303" s="2" t="inlineStr"/>
       <c r="L303" s="2" t="inlineStr"/>
       <c r="M303" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站云山路灵山路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="N303" s="2" t="inlineStr">
@@ -37888,7 +37924,7 @@
       </c>
       <c r="P303" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q303" s="2" t="inlineStr">
@@ -37912,12 +37948,12 @@
       </c>
       <c r="X303" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y303" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z303" s="2" t="inlineStr">
@@ -37937,12 +37973,12 @@
       </c>
       <c r="AC303" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AD303" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -37980,29 +38016,29 @@
       </c>
       <c r="H304" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I304" s="2" t="inlineStr">
         <is>
-          <t>22:07</t>
+          <t>22:06</t>
         </is>
       </c>
       <c r="J304" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="K304" s="2" t="inlineStr"/>
       <c r="L304" s="2" t="inlineStr"/>
       <c r="M304" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数87分钟估算，约±10分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N304" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O304" s="2" t="inlineStr">
@@ -38012,7 +38048,7 @@
       </c>
       <c r="P304" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q304" s="2" t="inlineStr">
@@ -38036,12 +38072,12 @@
       </c>
       <c r="X304" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y304" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z304" s="2" t="inlineStr">
@@ -38061,7 +38097,7 @@
       </c>
       <c r="AC304" s="2" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AD304" s="2" t="inlineStr">
@@ -38089,7 +38125,7 @@
       </c>
       <c r="E305" s="2" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="F305" s="2" t="inlineStr">
@@ -38109,7 +38145,7 @@
       </c>
       <c r="I305" s="2" t="inlineStr">
         <is>
-          <t>22:29</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="J305" s="2" t="inlineStr">
@@ -38136,7 +38172,7 @@
       </c>
       <c r="P305" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q305" s="2" t="inlineStr">
@@ -38150,7 +38186,7 @@
       <c r="U305" s="2" t="inlineStr"/>
       <c r="V305" s="2" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="W305" s="2" t="inlineStr">
@@ -38175,17 +38211,17 @@
       </c>
       <c r="AA305" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB305" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC305" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AD305" s="2" t="inlineStr">
@@ -38203,7 +38239,7 @@
       <c r="B306" s="2" t="inlineStr"/>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D306" s="2" t="inlineStr">
@@ -38233,34 +38269,34 @@
       </c>
       <c r="I306" s="2" t="inlineStr">
         <is>
-          <t>23:06</t>
+          <t>22:59</t>
         </is>
       </c>
       <c r="J306" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K306" s="2" t="inlineStr"/>
       <c r="L306" s="2" t="inlineStr"/>
       <c r="M306" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±12分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±8分钟</t>
         </is>
       </c>
       <c r="N306" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O306" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P306" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q306" s="2" t="inlineStr">
@@ -38284,37 +38320,285 @@
       </c>
       <c r="X306" s="2" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y306" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z306" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA306" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB306" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC306" s="2" t="inlineStr">
+        <is>
+          <t>82.7</t>
+        </is>
+      </c>
+      <c r="AD306" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B307" s="2" t="inlineStr"/>
+      <c r="C307" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D307" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E307" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="F307" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G307" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H307" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I307" s="2" t="inlineStr">
+        <is>
+          <t>22:58</t>
+        </is>
+      </c>
+      <c r="J307" s="2" t="inlineStr">
+        <is>
+          <t>78分钟</t>
+        </is>
+      </c>
+      <c r="K307" s="2" t="inlineStr"/>
+      <c r="L307" s="2" t="inlineStr"/>
+      <c r="M307" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="N307" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O307" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P307" s="2" t="inlineStr">
+        <is>
+          <t>21:20</t>
+        </is>
+      </c>
+      <c r="Q307" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R307" s="2" t="inlineStr"/>
+      <c r="S307" s="2" t="inlineStr"/>
+      <c r="T307" s="2" t="inlineStr"/>
+      <c r="U307" s="2" t="inlineStr"/>
+      <c r="V307" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="W307" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X307" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y307" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z307" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA307" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB307" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC307" s="2" t="inlineStr">
+        <is>
+          <t>80.7</t>
+        </is>
+      </c>
+      <c r="AD307" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B308" s="2" t="inlineStr"/>
+      <c r="C308" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D308" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E308" s="2" t="inlineStr">
+        <is>
+          <t>21:52</t>
+        </is>
+      </c>
+      <c r="F308" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G308" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H308" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I308" s="2" t="inlineStr">
+        <is>
+          <t>23:18</t>
+        </is>
+      </c>
+      <c r="J308" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="K308" s="2" t="inlineStr"/>
+      <c r="L308" s="2" t="inlineStr"/>
+      <c r="M308" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="N308" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="O308" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P308" s="2" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="Q308" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R308" s="2" t="inlineStr"/>
+      <c r="S308" s="2" t="inlineStr"/>
+      <c r="T308" s="2" t="inlineStr"/>
+      <c r="U308" s="2" t="inlineStr"/>
+      <c r="V308" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="W308" s="2" t="inlineStr">
+        <is>
+          <t>终点确认到达+2分钟（覆盖计划时间）</t>
+        </is>
+      </c>
+      <c r="X308" s="2" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="Y306" s="2" t="inlineStr">
+      <c r="Y308" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Z306" s="2" t="inlineStr">
+      <c r="Z308" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="AA306" s="2" t="inlineStr">
+      <c r="AA308" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AB306" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AC306" s="2" t="inlineStr">
-        <is>
-          <t>89.8</t>
-        </is>
-      </c>
-      <c r="AD306" s="2" t="inlineStr">
-        <is>
-          <t>10/18</t>
+      <c r="AB308" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC308" s="2" t="inlineStr">
+        <is>
+          <t>92.4</t>
+        </is>
+      </c>
+      <c r="AD308" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-20-operations.xlsx
+++ b/data/export/2026-09-20-operations.xlsx
@@ -1230,7 +1230,7 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1473,12 +1473,12 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2966,7 +2966,7 @@
       </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3209,12 +3209,12 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3338,7 +3338,7 @@
       </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3532,7 +3532,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4028,7 +4028,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -4077,12 +4077,12 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4941,12 +4941,12 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5512,7 +5512,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5561,12 +5561,12 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -6132,7 +6132,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -6256,7 +6256,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6504,7 +6504,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6553,12 +6553,12 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -7426,7 +7426,7 @@
       </c>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -7922,7 +7922,7 @@
       </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -8170,7 +8170,7 @@
       </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -8240,7 +8240,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -8608,7 +8608,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8856,7 +8856,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -9600,7 +9600,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9649,12 +9649,12 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -9778,7 +9778,7 @@
       </c>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -10150,7 +10150,7 @@
       </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -10220,7 +10220,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10344,7 +10344,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10393,12 +10393,12 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD80" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -10522,7 +10522,7 @@
       </c>
       <c r="AD81" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -11266,7 +11266,7 @@
       </c>
       <c r="AD87" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -11460,7 +11460,7 @@
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -11509,12 +11509,12 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AD89" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -11638,7 +11638,7 @@
       </c>
       <c r="AD90" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -11708,7 +11708,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11886,7 +11886,7 @@
       </c>
       <c r="AD92" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -12080,7 +12080,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -12129,12 +12129,12 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD94" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -12301,24 +12301,24 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>21:43</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr"/>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr">
@@ -12328,7 +12328,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12377,12 +12377,12 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AD96" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -12420,7 +12420,7 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
@@ -12437,10 +12437,14 @@
       <c r="L97" s="2" t="inlineStr"/>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：21:22采样，终点ETA 39分钟</t>
-        </is>
-      </c>
-      <c r="N97" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -12448,7 +12452,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12472,12 +12476,12 @@
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -12540,29 +12544,29 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>22:23</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr"/>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>21:22采样：该车到重点站长岛路台儿庄路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数71分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O98" s="2" t="inlineStr">
@@ -12572,7 +12576,7 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -12596,12 +12600,12 @@
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
@@ -12621,12 +12625,12 @@
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD98" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -12874,7 +12878,7 @@
       </c>
       <c r="AD100" s="2" t="inlineStr">
         <is>
-          <t>14/32</t>
+          <t>13/32</t>
         </is>
       </c>
     </row>
@@ -12998,7 +13002,7 @@
       </c>
       <c r="AD101" s="2" t="inlineStr">
         <is>
-          <t>7/32</t>
+          <t>6/32</t>
         </is>
       </c>
     </row>
@@ -13122,7 +13126,7 @@
       </c>
       <c r="AD102" s="2" t="inlineStr">
         <is>
-          <t>11/32</t>
+          <t>10/32</t>
         </is>
       </c>
     </row>
@@ -13324,7 +13328,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -13373,12 +13377,12 @@
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>132.8</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AD104" s="2" t="inlineStr">
         <is>
-          <t>5/32</t>
+          <t>6/32</t>
         </is>
       </c>
     </row>
@@ -13812,7 +13816,7 @@
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -13861,12 +13865,12 @@
       </c>
       <c r="AC108" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AD108" s="2" t="inlineStr">
         <is>
-          <t>12/32</t>
+          <t>11/32</t>
         </is>
       </c>
     </row>
@@ -14358,7 +14362,7 @@
       </c>
       <c r="AD112" s="2" t="inlineStr">
         <is>
-          <t>13/32</t>
+          <t>11/32</t>
         </is>
       </c>
     </row>
@@ -14564,7 +14568,7 @@
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q114" s="2" t="inlineStr">
@@ -14613,12 +14617,12 @@
       </c>
       <c r="AC114" s="2" t="inlineStr">
         <is>
-          <t>133.2</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AD114" s="2" t="inlineStr">
         <is>
-          <t>7/32</t>
+          <t>13/32</t>
         </is>
       </c>
     </row>
@@ -14866,7 +14870,7 @@
       </c>
       <c r="AD116" s="2" t="inlineStr">
         <is>
-          <t>9/32</t>
+          <t>8/32</t>
         </is>
       </c>
     </row>
@@ -14936,7 +14940,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -14985,12 +14989,12 @@
       </c>
       <c r="AC117" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AD117" s="2" t="inlineStr">
         <is>
-          <t>23/32</t>
+          <t>24/32</t>
         </is>
       </c>
     </row>
@@ -15180,7 +15184,7 @@
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
@@ -15229,7 +15233,7 @@
       </c>
       <c r="AC119" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.2</t>
         </is>
       </c>
       <c r="AD119" s="2" t="inlineStr">
@@ -15978,7 +15982,7 @@
       </c>
       <c r="AD125" s="2" t="inlineStr">
         <is>
-          <t>10/32</t>
+          <t>9/32</t>
         </is>
       </c>
     </row>
@@ -16048,7 +16052,7 @@
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
@@ -16350,7 +16354,7 @@
       </c>
       <c r="AD128" s="2" t="inlineStr">
         <is>
-          <t>14/32</t>
+          <t>13/32</t>
         </is>
       </c>
     </row>
@@ -16474,7 +16478,7 @@
       </c>
       <c r="AD129" s="2" t="inlineStr">
         <is>
-          <t>7/32</t>
+          <t>6/32</t>
         </is>
       </c>
     </row>
@@ -16598,7 +16602,7 @@
       </c>
       <c r="AD130" s="2" t="inlineStr">
         <is>
-          <t>11/32</t>
+          <t>10/32</t>
         </is>
       </c>
     </row>
@@ -16800,7 +16804,7 @@
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
@@ -16849,12 +16853,12 @@
       </c>
       <c r="AC132" s="2" t="inlineStr">
         <is>
-          <t>132.8</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AD132" s="2" t="inlineStr">
         <is>
-          <t>5/32</t>
+          <t>6/32</t>
         </is>
       </c>
     </row>
@@ -17288,7 +17292,7 @@
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q136" s="2" t="inlineStr">
@@ -17337,12 +17341,12 @@
       </c>
       <c r="AC136" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AD136" s="2" t="inlineStr">
         <is>
-          <t>12/32</t>
+          <t>11/32</t>
         </is>
       </c>
     </row>
@@ -17710,7 +17714,7 @@
       </c>
       <c r="AD139" s="2" t="inlineStr">
         <is>
-          <t>13/32</t>
+          <t>11/32</t>
         </is>
       </c>
     </row>
@@ -17900,7 +17904,7 @@
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q141" s="2" t="inlineStr">
@@ -17949,12 +17953,12 @@
       </c>
       <c r="AC141" s="2" t="inlineStr">
         <is>
-          <t>133.2</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AD141" s="2" t="inlineStr">
         <is>
-          <t>7/32</t>
+          <t>13/32</t>
         </is>
       </c>
     </row>
@@ -18002,7 +18006,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr"/>
@@ -18024,7 +18028,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="Q142" s="2" t="inlineStr">
@@ -18073,12 +18077,12 @@
       </c>
       <c r="AC142" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AD142" s="2" t="inlineStr">
         <is>
-          <t>23/32</t>
+          <t>24/32</t>
         </is>
       </c>
     </row>
@@ -18202,7 +18206,7 @@
       </c>
       <c r="AD143" s="2" t="inlineStr">
         <is>
-          <t>9/32</t>
+          <t>8/32</t>
         </is>
       </c>
     </row>
@@ -18392,7 +18396,7 @@
       </c>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q145" s="2" t="inlineStr">
@@ -18441,7 +18445,7 @@
       </c>
       <c r="AC145" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.2</t>
         </is>
       </c>
       <c r="AD145" s="2" t="inlineStr">
@@ -18814,7 +18818,7 @@
       </c>
       <c r="AD148" s="2" t="inlineStr">
         <is>
-          <t>10/32</t>
+          <t>9/32</t>
         </is>
       </c>
     </row>
@@ -18884,7 +18888,7 @@
       </c>
       <c r="P149" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q149" s="2" t="inlineStr">
@@ -19062,7 +19066,7 @@
       </c>
       <c r="AD150" s="2" t="inlineStr">
         <is>
-          <t>11/32</t>
+          <t>10/32</t>
         </is>
       </c>
     </row>
@@ -19186,7 +19190,7 @@
       </c>
       <c r="AD151" s="2" t="inlineStr">
         <is>
-          <t>7/32</t>
+          <t>6/32</t>
         </is>
       </c>
     </row>
@@ -19810,7 +19814,7 @@
       </c>
       <c r="AD156" s="2" t="inlineStr">
         <is>
-          <t>13/32</t>
+          <t>11/32</t>
         </is>
       </c>
     </row>
@@ -20178,7 +20182,7 @@
       </c>
       <c r="AD159" s="2" t="inlineStr">
         <is>
-          <t>9/32</t>
+          <t>8/32</t>
         </is>
       </c>
     </row>
@@ -20550,7 +20554,7 @@
       </c>
       <c r="AD162" s="2" t="inlineStr">
         <is>
-          <t>10/32</t>
+          <t>9/32</t>
         </is>
       </c>
     </row>
@@ -20798,7 +20802,7 @@
       </c>
       <c r="AD164" s="2" t="inlineStr">
         <is>
-          <t>11/32</t>
+          <t>10/32</t>
         </is>
       </c>
     </row>
@@ -21972,7 +21976,7 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -22021,12 +22025,12 @@
       </c>
       <c r="AC174" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AD174" s="2" t="inlineStr">
         <is>
-          <t>23/32</t>
+          <t>24/32</t>
         </is>
       </c>
     </row>
@@ -22464,7 +22468,7 @@
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q178" s="2" t="inlineStr">
@@ -22642,7 +22646,7 @@
       </c>
       <c r="AD179" s="2" t="inlineStr">
         <is>
-          <t>14/32</t>
+          <t>13/32</t>
         </is>
       </c>
     </row>
@@ -22712,7 +22716,7 @@
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="Q180" s="2" t="inlineStr">
@@ -22761,12 +22765,12 @@
       </c>
       <c r="AC180" s="2" t="inlineStr">
         <is>
-          <t>132.8</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AD180" s="2" t="inlineStr">
         <is>
-          <t>5/32</t>
+          <t>6/32</t>
         </is>
       </c>
     </row>
@@ -22886,7 +22890,7 @@
       </c>
       <c r="AD181" s="2" t="inlineStr">
         <is>
-          <t>7/32</t>
+          <t>6/32</t>
         </is>
       </c>
     </row>
@@ -22956,7 +22960,7 @@
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q182" s="2" t="inlineStr">
@@ -23005,12 +23009,12 @@
       </c>
       <c r="AC182" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AD182" s="2" t="inlineStr">
         <is>
-          <t>12/32</t>
+          <t>11/32</t>
         </is>
       </c>
     </row>
@@ -23382,7 +23386,7 @@
       </c>
       <c r="AD185" s="2" t="inlineStr">
         <is>
-          <t>13/32</t>
+          <t>11/32</t>
         </is>
       </c>
     </row>
@@ -23452,7 +23456,7 @@
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q186" s="2" t="inlineStr">
@@ -23501,12 +23505,12 @@
       </c>
       <c r="AC186" s="2" t="inlineStr">
         <is>
-          <t>133.2</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AD186" s="2" t="inlineStr">
         <is>
-          <t>7/32</t>
+          <t>13/32</t>
         </is>
       </c>
     </row>
@@ -23630,7 +23634,7 @@
       </c>
       <c r="AD187" s="2" t="inlineStr">
         <is>
-          <t>9/32</t>
+          <t>8/32</t>
         </is>
       </c>
     </row>
@@ -24188,7 +24192,7 @@
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q192" s="2" t="inlineStr">
@@ -24237,7 +24241,7 @@
       </c>
       <c r="AC192" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.2</t>
         </is>
       </c>
       <c r="AD192" s="2" t="inlineStr">
@@ -24998,7 +25002,7 @@
       </c>
       <c r="AD198" s="2" t="inlineStr">
         <is>
-          <t>14/32</t>
+          <t>13/32</t>
         </is>
       </c>
     </row>
@@ -25284,7 +25288,7 @@
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq55，推进27站，达到≥2站确认条件</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq60，推进32站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I201" s="2" t="inlineStr">
@@ -25312,7 +25316,7 @@
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q201" s="2" t="inlineStr">
@@ -25420,29 +25424,29 @@
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I202" s="2" t="inlineStr">
         <is>
-          <t>21:41</t>
+          <t>21:43</t>
         </is>
       </c>
       <c r="J202" s="2" t="inlineStr">
         <is>
-          <t>121分钟</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="K202" s="2" t="inlineStr"/>
       <c r="L202" s="2" t="inlineStr"/>
       <c r="M202" s="2" t="inlineStr">
         <is>
-          <t>21:20采样：该车到重点站东波路莱阳路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数16分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N202" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O202" s="2" t="inlineStr">
@@ -25452,7 +25456,7 @@
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="Q202" s="2" t="inlineStr">
@@ -25476,12 +25480,12 @@
       </c>
       <c r="X202" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y202" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z202" s="2" t="inlineStr">
@@ -25501,12 +25505,12 @@
       </c>
       <c r="AC202" s="2" t="inlineStr">
         <is>
-          <t>132.8</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AD202" s="2" t="inlineStr">
         <is>
-          <t>5/32</t>
+          <t>6/32</t>
         </is>
       </c>
     </row>
@@ -25576,7 +25580,7 @@
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="Q203" s="2" t="inlineStr">
@@ -25625,12 +25629,12 @@
       </c>
       <c r="AC203" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AD203" s="2" t="inlineStr">
         <is>
-          <t>23/32</t>
+          <t>24/32</t>
         </is>
       </c>
     </row>
@@ -25668,29 +25672,29 @@
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I204" s="2" t="inlineStr">
         <is>
-          <t>22:04</t>
+          <t>22:06</t>
         </is>
       </c>
       <c r="J204" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K204" s="2" t="inlineStr"/>
       <c r="L204" s="2" t="inlineStr"/>
       <c r="M204" s="2" t="inlineStr">
         <is>
-          <t>21:20采样：该车到重点站沪南路御桥路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N204" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O204" s="2" t="inlineStr">
@@ -25700,7 +25704,7 @@
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q204" s="2" t="inlineStr">
@@ -25724,12 +25728,12 @@
       </c>
       <c r="X204" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y204" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z204" s="2" t="inlineStr">
@@ -25749,7 +25753,7 @@
       </c>
       <c r="AC204" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AD204" s="2" t="inlineStr">
@@ -25792,29 +25796,29 @@
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I205" s="2" t="inlineStr">
         <is>
-          <t>22:06</t>
+          <t>22:09</t>
         </is>
       </c>
       <c r="J205" s="2" t="inlineStr">
         <is>
-          <t>122分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="K205" s="2" t="inlineStr"/>
       <c r="L205" s="2" t="inlineStr"/>
       <c r="M205" s="2" t="inlineStr">
         <is>
-          <t>21:20采样：该车到重点站云山路碧云路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数46分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="N205" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O205" s="2" t="inlineStr">
@@ -25824,7 +25828,7 @@
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q205" s="2" t="inlineStr">
@@ -25848,12 +25852,12 @@
       </c>
       <c r="X205" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y205" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z205" s="2" t="inlineStr">
@@ -25873,12 +25877,12 @@
       </c>
       <c r="AC205" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AD205" s="2" t="inlineStr">
         <is>
-          <t>12/32</t>
+          <t>11/32</t>
         </is>
       </c>
     </row>
@@ -25921,26 +25925,22 @@
       </c>
       <c r="I206" s="2" t="inlineStr">
         <is>
-          <t>22:24</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="J206" s="2" t="inlineStr">
         <is>
-          <t>115分钟</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="K206" s="2" t="inlineStr"/>
       <c r="L206" s="2" t="inlineStr"/>
       <c r="M206" s="2" t="inlineStr">
         <is>
-          <t>21:20采样：该车到重点站锦绣路花木路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数61分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N206" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：21:51采样，终点ETA 42分钟</t>
+        </is>
+      </c>
+      <c r="N206" s="2" t="inlineStr"/>
       <c r="O206" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -25948,7 +25948,7 @@
       </c>
       <c r="P206" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q206" s="2" t="inlineStr">
@@ -25972,12 +25972,12 @@
       </c>
       <c r="X206" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y206" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z206" s="2" t="inlineStr">
@@ -25997,12 +25997,12 @@
       </c>
       <c r="AC206" s="2" t="inlineStr">
         <is>
-          <t>133.2</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AD206" s="2" t="inlineStr">
         <is>
-          <t>7/32</t>
+          <t>13/32</t>
         </is>
       </c>
     </row>
@@ -26045,19 +26045,19 @@
       </c>
       <c r="I207" s="2" t="inlineStr">
         <is>
-          <t>22:54</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="J207" s="2" t="inlineStr">
         <is>
-          <t>120分钟</t>
+          <t>117分钟</t>
         </is>
       </c>
       <c r="K207" s="2" t="inlineStr"/>
       <c r="L207" s="2" t="inlineStr"/>
       <c r="M207" s="2" t="inlineStr">
         <is>
-          <t>21:20采样：该车到重点站康沈路秀康路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数94分钟，约±5分钟</t>
+          <t>21:51采样：该车到重点站迎春路金松路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N207" s="2" t="inlineStr">
@@ -26072,7 +26072,7 @@
       </c>
       <c r="P207" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q207" s="2" t="inlineStr">
@@ -26121,7 +26121,7 @@
       </c>
       <c r="AC207" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.2</t>
         </is>
       </c>
       <c r="AD207" s="2" t="inlineStr">
@@ -26192,7 +26192,7 @@
       </c>
       <c r="P208" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q208" s="2" t="inlineStr">
@@ -26241,12 +26241,12 @@
       </c>
       <c r="AC208" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AD208" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -26610,7 +26610,7 @@
       </c>
       <c r="AD211" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -26676,7 +26676,7 @@
       </c>
       <c r="P212" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q212" s="2" t="inlineStr">
@@ -26725,12 +26725,12 @@
       </c>
       <c r="AC212" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AD212" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -27226,7 +27226,7 @@
       </c>
       <c r="AD216" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AD218" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -27668,7 +27668,7 @@
       </c>
       <c r="P220" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q220" s="2" t="inlineStr">
@@ -27717,12 +27717,12 @@
       </c>
       <c r="AC220" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD220" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -27842,7 +27842,7 @@
       </c>
       <c r="AD221" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -28160,7 +28160,7 @@
       </c>
       <c r="P224" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q224" s="2" t="inlineStr">
@@ -28209,12 +28209,12 @@
       </c>
       <c r="AC224" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AD224" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -28702,7 +28702,7 @@
       </c>
       <c r="AD228" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -29136,7 +29136,7 @@
       </c>
       <c r="P232" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q232" s="2" t="inlineStr">
@@ -29185,12 +29185,12 @@
       </c>
       <c r="AC232" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AD232" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -29508,7 +29508,7 @@
       </c>
       <c r="P235" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q235" s="2" t="inlineStr">
@@ -29557,12 +29557,12 @@
       </c>
       <c r="AC235" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD235" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -29686,7 +29686,7 @@
       </c>
       <c r="AD236" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -29930,7 +29930,7 @@
       </c>
       <c r="AD238" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -30558,7 +30558,7 @@
       </c>
       <c r="AD243" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -31008,7 +31008,7 @@
       </c>
       <c r="P247" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q247" s="2" t="inlineStr">
@@ -31057,12 +31057,12 @@
       </c>
       <c r="AC247" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD247" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -31186,7 +31186,7 @@
       </c>
       <c r="AD248" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -31806,7 +31806,7 @@
       </c>
       <c r="AD253" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -32124,7 +32124,7 @@
       </c>
       <c r="P256" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q256" s="2" t="inlineStr">
@@ -32173,12 +32173,12 @@
       </c>
       <c r="AC256" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD256" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -32302,7 +32302,7 @@
       </c>
       <c r="AD257" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -32922,7 +32922,7 @@
       </c>
       <c r="AD262" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -32992,7 +32992,7 @@
       </c>
       <c r="P263" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q263" s="2" t="inlineStr">
@@ -33041,12 +33041,12 @@
       </c>
       <c r="AC263" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AD263" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -33418,7 +33418,7 @@
       </c>
       <c r="AD266" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -33538,7 +33538,7 @@
       </c>
       <c r="AD267" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -33732,7 +33732,7 @@
       </c>
       <c r="P269" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q269" s="2" t="inlineStr">
@@ -33781,12 +33781,12 @@
       </c>
       <c r="AC269" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AD269" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -34030,7 +34030,7 @@
       </c>
       <c r="AD271" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -34774,7 +34774,7 @@
       </c>
       <c r="AD277" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -34964,7 +34964,7 @@
       </c>
       <c r="P279" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q279" s="2" t="inlineStr">
@@ -35013,12 +35013,12 @@
       </c>
       <c r="AC279" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AD279" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -35142,7 +35142,7 @@
       </c>
       <c r="AD280" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -35510,7 +35510,7 @@
       </c>
       <c r="AD283" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -35700,7 +35700,7 @@
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q285" s="2" t="inlineStr">
@@ -35749,12 +35749,12 @@
       </c>
       <c r="AC285" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AD285" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -35878,7 +35878,7 @@
       </c>
       <c r="AD286" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -35948,7 +35948,7 @@
       </c>
       <c r="P287" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q287" s="2" t="inlineStr">
@@ -35997,12 +35997,12 @@
       </c>
       <c r="AC287" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD287" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -36870,7 +36870,7 @@
       </c>
       <c r="AD294" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -36994,7 +36994,7 @@
       </c>
       <c r="AD295" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -37064,7 +37064,7 @@
       </c>
       <c r="P296" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q296" s="2" t="inlineStr">
@@ -37113,12 +37113,12 @@
       </c>
       <c r="AC296" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AD296" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -37366,7 +37366,7 @@
       </c>
       <c r="AD298" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -37436,7 +37436,7 @@
       </c>
       <c r="P299" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q299" s="2" t="inlineStr">
@@ -37485,12 +37485,12 @@
       </c>
       <c r="AC299" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD299" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -37560,7 +37560,7 @@
       </c>
       <c r="P300" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q300" s="2" t="inlineStr">
@@ -37609,12 +37609,12 @@
       </c>
       <c r="AC300" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AD300" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -37854,7 +37854,7 @@
       </c>
       <c r="AD302" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -38021,24 +38021,24 @@
       </c>
       <c r="I304" s="2" t="inlineStr">
         <is>
-          <t>22:06</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="J304" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K304" s="2" t="inlineStr"/>
       <c r="L304" s="2" t="inlineStr"/>
       <c r="M304" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="N304" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O304" s="2" t="inlineStr">
@@ -38048,7 +38048,7 @@
       </c>
       <c r="P304" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q304" s="2" t="inlineStr">
@@ -38097,12 +38097,12 @@
       </c>
       <c r="AC304" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AD304" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -38157,12 +38157,12 @@
       <c r="L305" s="2" t="inlineStr"/>
       <c r="M305" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±8分钟</t>
+          <t>21:50采样：该车到重点站金高路东靖路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数40分钟，约±7分钟</t>
         </is>
       </c>
       <c r="N305" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O305" s="2" t="inlineStr">
@@ -38172,7 +38172,7 @@
       </c>
       <c r="P305" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q305" s="2" t="inlineStr">
@@ -38201,7 +38201,7 @@
       </c>
       <c r="Y305" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z305" s="2" t="inlineStr">
@@ -38221,12 +38221,12 @@
       </c>
       <c r="AC305" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AD305" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -38264,29 +38264,29 @@
       </c>
       <c r="H306" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I306" s="2" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="J306" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>50分钟</t>
         </is>
       </c>
       <c r="K306" s="2" t="inlineStr"/>
       <c r="L306" s="2" t="inlineStr"/>
       <c r="M306" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±8分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N306" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O306" s="2" t="inlineStr">
@@ -38296,7 +38296,7 @@
       </c>
       <c r="P306" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q306" s="2" t="inlineStr">
@@ -38320,12 +38320,12 @@
       </c>
       <c r="X306" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y306" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z306" s="2" t="inlineStr">
@@ -38345,12 +38345,12 @@
       </c>
       <c r="AC306" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AD306" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -38393,24 +38393,24 @@
       </c>
       <c r="I307" s="2" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="J307" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K307" s="2" t="inlineStr"/>
       <c r="L307" s="2" t="inlineStr"/>
       <c r="M307" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±8分钟</t>
+          <t>21:50采样：该车到重点站金杨路云山路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±7分钟</t>
         </is>
       </c>
       <c r="N307" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O307" s="2" t="inlineStr">
@@ -38420,7 +38420,7 @@
       </c>
       <c r="P307" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q307" s="2" t="inlineStr">
@@ -38449,7 +38449,7 @@
       </c>
       <c r="Y307" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z307" s="2" t="inlineStr">
@@ -38469,12 +38469,12 @@
       </c>
       <c r="AC307" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD307" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -38598,7 +38598,7 @@
       </c>
       <c r="AD308" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
